--- a/research/traditional_assets/database/data/curacao/curacao_diversified.xlsx
+++ b/research/traditional_assets/database/data/curacao/curacao_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09870140279631869</v>
+        <v>0.09851935971016679</v>
       </c>
       <c r="C2">
-        <v>16139.92560692971</v>
+        <v>16003.98972659223</v>
       </c>
       <c r="D2">
-        <v>13278.82560692971</v>
+        <v>13304.31472659223</v>
       </c>
       <c r="E2">
-        <v>-5348.8</v>
+        <v>-5187.375</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>161.425</v>
       </c>
       <c r="G2">
         <v>2861.1</v>
@@ -1451,28 +1451,28 @@
         <v>1787.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>8.1196775</v>
       </c>
       <c r="N2">
-        <v>1787.2</v>
+        <v>1779.0803225</v>
       </c>
       <c r="O2">
-        <v>393.184</v>
+        <v>391.39767095</v>
       </c>
       <c r="P2">
-        <v>1394.016</v>
+        <v>1387.68265155</v>
       </c>
       <c r="Q2">
-        <v>2537.716</v>
+        <v>2531.38265155</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09870140279631869</v>
+        <v>0.09911820172744119</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429367</v>
+        <v>0.7339451160150325</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>220.1072641123986</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09851935971016679</v>
+        <v>0.09833731662401488</v>
       </c>
       <c r="C3">
-        <v>16003.98972659223</v>
+        <v>15868.15188876983</v>
       </c>
       <c r="D3">
-        <v>13304.31472659223</v>
+        <v>13329.90188876983</v>
       </c>
       <c r="E3">
-        <v>-5187.375</v>
+        <v>-5025.95</v>
       </c>
       <c r="F3">
-        <v>161.425</v>
+        <v>322.85</v>
       </c>
       <c r="G3">
         <v>2861.1</v>
@@ -1533,28 +1533,28 @@
         <v>1787.2</v>
       </c>
       <c r="M3">
-        <v>8.1196775</v>
+        <v>16.239355</v>
       </c>
       <c r="N3">
-        <v>1779.0803225</v>
+        <v>1770.960645</v>
       </c>
       <c r="O3">
-        <v>391.39767095</v>
+        <v>389.6113419</v>
       </c>
       <c r="P3">
-        <v>1387.68265155</v>
+        <v>1381.3493031</v>
       </c>
       <c r="Q3">
-        <v>2531.38265155</v>
+        <v>2525.0493031</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09911820172744119</v>
+        <v>0.09954350675919886</v>
       </c>
       <c r="T3">
-        <v>0.7339451160150325</v>
+        <v>0.7397995998641099</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>220.1072641123986</v>
+        <v>110.0536320561993</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09833731662401488</v>
+        <v>0.09815527353786298</v>
       </c>
       <c r="C4">
-        <v>15868.15188876983</v>
+        <v>15732.41266022532</v>
       </c>
       <c r="D4">
-        <v>13329.90188876983</v>
+        <v>13355.58766022532</v>
       </c>
       <c r="E4">
-        <v>-5025.95</v>
+        <v>-4864.525000000001</v>
       </c>
       <c r="F4">
-        <v>322.85</v>
+        <v>484.275</v>
       </c>
       <c r="G4">
         <v>2861.1</v>
@@ -1615,28 +1615,28 @@
         <v>1787.2</v>
       </c>
       <c r="M4">
-        <v>16.239355</v>
+        <v>24.3590325</v>
       </c>
       <c r="N4">
-        <v>1770.960645</v>
+        <v>1762.8409675</v>
       </c>
       <c r="O4">
-        <v>389.6113419</v>
+        <v>387.82501285</v>
       </c>
       <c r="P4">
-        <v>1381.3493031</v>
+        <v>1375.01595465</v>
       </c>
       <c r="Q4">
-        <v>2525.0493031</v>
+        <v>2518.71595465</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09954350675919886</v>
+        <v>0.09997758096686905</v>
       </c>
       <c r="T4">
-        <v>0.7397995998641099</v>
+        <v>0.7457747947203849</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>110.0536320561993</v>
+        <v>73.3690880374662</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09815527353786298</v>
+        <v>0.09797323045171109</v>
       </c>
       <c r="C5">
-        <v>15732.41266022532</v>
+        <v>15596.77261209843</v>
       </c>
       <c r="D5">
-        <v>13355.58766022532</v>
+        <v>13381.37261209843</v>
       </c>
       <c r="E5">
-        <v>-4864.525000000001</v>
+        <v>-4703.1</v>
       </c>
       <c r="F5">
-        <v>484.275</v>
+        <v>645.7</v>
       </c>
       <c r="G5">
         <v>2861.1</v>
@@ -1697,28 +1697,28 @@
         <v>1787.2</v>
       </c>
       <c r="M5">
-        <v>24.3590325</v>
+        <v>32.47871</v>
       </c>
       <c r="N5">
-        <v>1762.8409675</v>
+        <v>1754.72129</v>
       </c>
       <c r="O5">
-        <v>387.82501285</v>
+        <v>386.0386838</v>
       </c>
       <c r="P5">
-        <v>1375.01595465</v>
+        <v>1368.6826062</v>
       </c>
       <c r="Q5">
-        <v>2518.71595465</v>
+        <v>2512.3826062</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09997758096686905</v>
+        <v>0.1004206983871991</v>
       </c>
       <c r="T5">
-        <v>0.7457747947203849</v>
+        <v>0.7518744728028322</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.3690880374662</v>
+        <v>55.02681602809964</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09797323045171109</v>
+        <v>0.09779118736555917</v>
       </c>
       <c r="C6">
-        <v>15596.77261209843</v>
+        <v>15461.23231994808</v>
       </c>
       <c r="D6">
-        <v>13381.37261209843</v>
+        <v>13407.25731994808</v>
       </c>
       <c r="E6">
-        <v>-4703.1</v>
+        <v>-4541.675</v>
       </c>
       <c r="F6">
-        <v>645.7</v>
+        <v>807.125</v>
       </c>
       <c r="G6">
         <v>2861.1</v>
@@ -1779,28 +1779,28 @@
         <v>1787.2</v>
       </c>
       <c r="M6">
-        <v>32.47871</v>
+        <v>40.5983875</v>
       </c>
       <c r="N6">
-        <v>1754.72129</v>
+        <v>1746.6016125</v>
       </c>
       <c r="O6">
-        <v>386.0386838</v>
+        <v>384.2523547500001</v>
       </c>
       <c r="P6">
-        <v>1368.6826062</v>
+        <v>1362.34925775</v>
       </c>
       <c r="Q6">
-        <v>2512.3826062</v>
+        <v>2506.04925775</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1004206983871991</v>
+        <v>0.1008731445953255</v>
       </c>
       <c r="T6">
-        <v>0.7518744728028322</v>
+        <v>0.7581025651606994</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.02681602809964</v>
+        <v>44.02145282247971</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09779118736555917</v>
+        <v>0.09760914427940727</v>
       </c>
       <c r="C7">
-        <v>15461.23231994808</v>
+        <v>15325.79236379523</v>
       </c>
       <c r="D7">
-        <v>13407.25731994808</v>
+        <v>13433.24236379523</v>
       </c>
       <c r="E7">
-        <v>-4541.675</v>
+        <v>-4380.25</v>
       </c>
       <c r="F7">
-        <v>807.125</v>
+        <v>968.5500000000001</v>
       </c>
       <c r="G7">
         <v>2861.1</v>
@@ -1861,28 +1861,28 @@
         <v>1787.2</v>
       </c>
       <c r="M7">
-        <v>40.5983875</v>
+        <v>48.718065</v>
       </c>
       <c r="N7">
-        <v>1746.6016125</v>
+        <v>1738.481935</v>
       </c>
       <c r="O7">
-        <v>384.2523547500001</v>
+        <v>382.4660257</v>
       </c>
       <c r="P7">
-        <v>1362.34925775</v>
+        <v>1356.0159093</v>
       </c>
       <c r="Q7">
-        <v>2506.04925775</v>
+        <v>2499.7159093</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1008731445953255</v>
+        <v>0.1013352173185184</v>
       </c>
       <c r="T7">
-        <v>0.7581025651606994</v>
+        <v>0.7644631701219254</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.02145282247971</v>
+        <v>36.68454401873309</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09760914427940727</v>
+        <v>0.09742710119325537</v>
       </c>
       <c r="C8">
-        <v>15325.79236379523</v>
+        <v>15190.45332816619</v>
       </c>
       <c r="D8">
-        <v>13433.24236379523</v>
+        <v>13459.32832816619</v>
       </c>
       <c r="E8">
-        <v>-4380.25</v>
+        <v>-4218.825000000001</v>
       </c>
       <c r="F8">
-        <v>968.55</v>
+        <v>1129.975</v>
       </c>
       <c r="G8">
         <v>2861.1</v>
@@ -1943,28 +1943,28 @@
         <v>1787.2</v>
       </c>
       <c r="M8">
-        <v>48.718065</v>
+        <v>56.83774249999999</v>
       </c>
       <c r="N8">
-        <v>1738.481935</v>
+        <v>1730.3622575</v>
       </c>
       <c r="O8">
-        <v>382.4660257</v>
+        <v>380.67969665</v>
       </c>
       <c r="P8">
-        <v>1356.0159093</v>
+        <v>1349.68256085</v>
       </c>
       <c r="Q8">
-        <v>2499.7159093</v>
+        <v>2493.38256085</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1013352173185184</v>
+        <v>0.1018072270895219</v>
       </c>
       <c r="T8">
-        <v>0.7644631701219254</v>
+        <v>0.7709605622866187</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.68454401873309</v>
+        <v>31.4438948731998</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09742710119325539</v>
+        <v>0.09724505810710347</v>
       </c>
       <c r="C9">
-        <v>15190.45332816618</v>
+        <v>15055.21580213648</v>
       </c>
       <c r="D9">
-        <v>13459.32832816618</v>
+        <v>13485.51580213648</v>
       </c>
       <c r="E9">
-        <v>-4218.825</v>
+        <v>-4057.4</v>
       </c>
       <c r="F9">
-        <v>1129.975</v>
+        <v>1291.4</v>
       </c>
       <c r="G9">
         <v>2861.1</v>
@@ -2025,28 +2025,28 @@
         <v>1787.2</v>
       </c>
       <c r="M9">
-        <v>56.8377425</v>
+        <v>64.95742</v>
       </c>
       <c r="N9">
-        <v>1730.3622575</v>
+        <v>1722.24258</v>
       </c>
       <c r="O9">
-        <v>380.67969665</v>
+        <v>378.8933676</v>
       </c>
       <c r="P9">
-        <v>1349.68256085</v>
+        <v>1343.3492124</v>
       </c>
       <c r="Q9">
-        <v>2493.38256085</v>
+        <v>2487.0492124</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1018072270895219</v>
+        <v>0.1022894979425038</v>
       </c>
       <c r="T9">
-        <v>0.7709605622866189</v>
+        <v>0.7775992021070662</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.44389487319979</v>
+        <v>27.51340801404982</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09724505810710347</v>
+        <v>0.09706301502095159</v>
       </c>
       <c r="C10">
-        <v>15055.21580213648</v>
+        <v>14920.08037937516</v>
       </c>
       <c r="D10">
-        <v>13485.51580213648</v>
+        <v>13511.80537937516</v>
       </c>
       <c r="E10">
-        <v>-4057.4</v>
+        <v>-3895.975</v>
       </c>
       <c r="F10">
-        <v>1291.4</v>
+        <v>1452.825</v>
       </c>
       <c r="G10">
         <v>2861.1</v>
@@ -2107,28 +2107,28 @@
         <v>1787.2</v>
       </c>
       <c r="M10">
-        <v>64.95742</v>
+        <v>73.07709749999999</v>
       </c>
       <c r="N10">
-        <v>1722.24258</v>
+        <v>1714.1229025</v>
       </c>
       <c r="O10">
-        <v>378.8933676</v>
+        <v>377.10703855</v>
       </c>
       <c r="P10">
-        <v>1343.3492124</v>
+        <v>1337.01586395</v>
       </c>
       <c r="Q10">
-        <v>2487.0492124</v>
+        <v>2480.71586395</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1022894979425038</v>
+        <v>0.1027823681548918</v>
       </c>
       <c r="T10">
-        <v>0.7775992021070662</v>
+        <v>0.7843837460993919</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.51340801404982</v>
+        <v>24.4563626791554</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09706301502095159</v>
+        <v>0.09688097193479966</v>
       </c>
       <c r="C11">
-        <v>14920.08037937516</v>
+        <v>14785.04765818968</v>
       </c>
       <c r="D11">
-        <v>13511.80537937516</v>
+        <v>13538.19765818968</v>
       </c>
       <c r="E11">
-        <v>-3895.975</v>
+        <v>-3734.55</v>
       </c>
       <c r="F11">
-        <v>1452.825</v>
+        <v>1614.25</v>
       </c>
       <c r="G11">
         <v>2861.1</v>
@@ -2189,28 +2189,28 @@
         <v>1787.2</v>
       </c>
       <c r="M11">
-        <v>73.07709749999999</v>
+        <v>81.19677499999999</v>
       </c>
       <c r="N11">
-        <v>1714.1229025</v>
+        <v>1706.003225</v>
       </c>
       <c r="O11">
-        <v>377.10703855</v>
+        <v>375.3207095</v>
       </c>
       <c r="P11">
-        <v>1337.01586395</v>
+        <v>1330.6825155</v>
       </c>
       <c r="Q11">
-        <v>2480.71586395</v>
+        <v>2474.3825155</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1027823681548918</v>
+        <v>0.1032861910386663</v>
       </c>
       <c r="T11">
-        <v>0.7843837460993919</v>
+        <v>0.7913190577359912</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.4563626791554</v>
+        <v>22.01072641123986</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09688097193479966</v>
+        <v>0.09669892884864778</v>
       </c>
       <c r="C12">
-        <v>14785.04765818968</v>
+        <v>14650.11824157126</v>
       </c>
       <c r="D12">
-        <v>13538.19765818968</v>
+        <v>13564.69324157126</v>
       </c>
       <c r="E12">
-        <v>-3734.55</v>
+        <v>-3573.125</v>
       </c>
       <c r="F12">
-        <v>1614.25</v>
+        <v>1775.675</v>
       </c>
       <c r="G12">
         <v>2861.1</v>
@@ -2271,28 +2271,28 @@
         <v>1787.2</v>
       </c>
       <c r="M12">
-        <v>81.196775</v>
+        <v>89.3164525</v>
       </c>
       <c r="N12">
-        <v>1706.003225</v>
+        <v>1697.8835475</v>
       </c>
       <c r="O12">
-        <v>375.3207095</v>
+        <v>373.53438045</v>
       </c>
       <c r="P12">
-        <v>1330.6825155</v>
+        <v>1324.34916705</v>
       </c>
       <c r="Q12">
-        <v>2474.3825155</v>
+        <v>2468.04916705</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1032861910386663</v>
+        <v>0.1038013357849975</v>
       </c>
       <c r="T12">
-        <v>0.7913190577359912</v>
+        <v>0.7984102190722896</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.01072641123985</v>
+        <v>20.00975128294532</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09669892884864778</v>
+        <v>0.09651688576249588</v>
       </c>
       <c r="C13">
-        <v>14650.11824157126</v>
+        <v>14515.29273724085</v>
       </c>
       <c r="D13">
-        <v>13564.69324157126</v>
+        <v>13591.29273724085</v>
       </c>
       <c r="E13">
-        <v>-3573.125</v>
+        <v>-3411.7</v>
       </c>
       <c r="F13">
-        <v>1775.675</v>
+        <v>1937.1</v>
       </c>
       <c r="G13">
         <v>2861.1</v>
@@ -2353,28 +2353,28 @@
         <v>1787.2</v>
       </c>
       <c r="M13">
-        <v>89.3164525</v>
+        <v>97.43612999999999</v>
       </c>
       <c r="N13">
-        <v>1697.8835475</v>
+        <v>1689.76387</v>
       </c>
       <c r="O13">
-        <v>373.53438045</v>
+        <v>371.7480514</v>
       </c>
       <c r="P13">
-        <v>1324.34916705</v>
+        <v>1318.0158186</v>
       </c>
       <c r="Q13">
-        <v>2468.04916705</v>
+        <v>2461.7158186</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1038013357849975</v>
+        <v>0.1043281883664726</v>
       </c>
       <c r="T13">
-        <v>0.7984102190722896</v>
+        <v>0.8056625431662309</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.00975128294532</v>
+        <v>18.34227200936655</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09651688576249588</v>
+        <v>0.09633484267634397</v>
       </c>
       <c r="C14">
-        <v>14515.29273724085</v>
+        <v>14380.57175769556</v>
       </c>
       <c r="D14">
-        <v>13591.29273724085</v>
+        <v>13617.99675769556</v>
       </c>
       <c r="E14">
-        <v>-3411.7</v>
+        <v>-3250.275</v>
       </c>
       <c r="F14">
-        <v>1937.1</v>
+        <v>2098.525</v>
       </c>
       <c r="G14">
         <v>2861.1</v>
@@ -2435,28 +2435,28 @@
         <v>1787.2</v>
       </c>
       <c r="M14">
-        <v>97.43612999999999</v>
+        <v>105.5558075</v>
       </c>
       <c r="N14">
-        <v>1689.76387</v>
+        <v>1681.6441925</v>
       </c>
       <c r="O14">
-        <v>371.7480514</v>
+        <v>369.9617223500001</v>
       </c>
       <c r="P14">
-        <v>1318.0158186</v>
+        <v>1311.68247015</v>
       </c>
       <c r="Q14">
-        <v>2461.7158186</v>
+        <v>2455.38247015</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1043281883664726</v>
+        <v>0.1048671525015448</v>
       </c>
       <c r="T14">
-        <v>0.8056625431662309</v>
+        <v>0.8130815873542858</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.34227200936655</v>
+        <v>16.93132800864604</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09633484267634397</v>
+        <v>0.09615279959019207</v>
       </c>
       <c r="C15">
-        <v>14380.57175769556</v>
+        <v>14245.95592025569</v>
       </c>
       <c r="D15">
-        <v>13617.99675769556</v>
+        <v>13644.80592025569</v>
       </c>
       <c r="E15">
-        <v>-3250.275</v>
+        <v>-3088.85</v>
       </c>
       <c r="F15">
-        <v>2098.525</v>
+        <v>2259.95</v>
       </c>
       <c r="G15">
         <v>2861.1</v>
@@ -2517,28 +2517,28 @@
         <v>1787.2</v>
       </c>
       <c r="M15">
-        <v>105.5558075</v>
+        <v>113.675485</v>
       </c>
       <c r="N15">
-        <v>1681.6441925</v>
+        <v>1673.524515</v>
       </c>
       <c r="O15">
-        <v>369.9617223500001</v>
+        <v>368.1753933</v>
       </c>
       <c r="P15">
-        <v>1311.68247015</v>
+        <v>1305.3491217</v>
       </c>
       <c r="Q15">
-        <v>2455.38247015</v>
+        <v>2449.0491217</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1048671525015448</v>
+        <v>0.1054186506862698</v>
       </c>
       <c r="T15">
-        <v>0.8130815873542858</v>
+        <v>0.820673167453691</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.93132800864604</v>
+        <v>15.7219474365999</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09615279959019207</v>
+        <v>0.09597075650404019</v>
       </c>
       <c r="C16">
-        <v>14245.95592025569</v>
+        <v>14111.4458471123</v>
       </c>
       <c r="D16">
-        <v>13644.80592025569</v>
+        <v>13671.7208471123</v>
       </c>
       <c r="E16">
-        <v>-3088.85</v>
+        <v>-2927.425</v>
       </c>
       <c r="F16">
-        <v>2259.95</v>
+        <v>2421.375</v>
       </c>
       <c r="G16">
         <v>2861.1</v>
@@ -2599,28 +2599,28 @@
         <v>1787.2</v>
       </c>
       <c r="M16">
-        <v>113.675485</v>
+        <v>121.7951625</v>
       </c>
       <c r="N16">
-        <v>1673.524515</v>
+        <v>1665.4048375</v>
       </c>
       <c r="O16">
-        <v>368.1753933</v>
+        <v>366.38906425</v>
       </c>
       <c r="P16">
-        <v>1305.3491217</v>
+        <v>1299.01577325</v>
       </c>
       <c r="Q16">
-        <v>2449.0491217</v>
+        <v>2442.71577325</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1054186506862698</v>
+        <v>0.1059831252988708</v>
       </c>
       <c r="T16">
-        <v>0.820673167453691</v>
+        <v>0.8284433729671998</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.7219474365999</v>
+        <v>14.67381760749323</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09597075650404019</v>
+        <v>0.09578871341788826</v>
       </c>
       <c r="C17">
-        <v>14111.4458471123</v>
+        <v>13977.04216537535</v>
       </c>
       <c r="D17">
-        <v>13671.7208471123</v>
+        <v>13698.74216537535</v>
       </c>
       <c r="E17">
-        <v>-2927.425</v>
+        <v>-2766</v>
       </c>
       <c r="F17">
-        <v>2421.375</v>
+        <v>2582.8</v>
       </c>
       <c r="G17">
         <v>2861.1</v>
@@ -2681,28 +2681,28 @@
         <v>1787.2</v>
       </c>
       <c r="M17">
-        <v>121.7951625</v>
+        <v>129.91484</v>
       </c>
       <c r="N17">
-        <v>1665.4048375</v>
+        <v>1657.28516</v>
       </c>
       <c r="O17">
-        <v>366.38906425</v>
+        <v>364.6027352</v>
       </c>
       <c r="P17">
-        <v>1299.01577325</v>
+        <v>1292.6824248</v>
       </c>
       <c r="Q17">
-        <v>2442.71577325</v>
+        <v>2436.3824248</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1059831252988708</v>
+        <v>0.1065610397832003</v>
       </c>
       <c r="T17">
-        <v>0.8284433729671998</v>
+        <v>0.8363985833738873</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.67381760749324</v>
+        <v>13.75670400702491</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09578871341788826</v>
+        <v>0.09560667033173638</v>
       </c>
       <c r="C18">
-        <v>13977.04216537535</v>
+        <v>13842.74550712236</v>
       </c>
       <c r="D18">
-        <v>13698.74216537535</v>
+        <v>13725.87050712236</v>
       </c>
       <c r="E18">
-        <v>-2766</v>
+        <v>-2604.575</v>
       </c>
       <c r="F18">
-        <v>2582.8</v>
+        <v>2744.225</v>
       </c>
       <c r="G18">
         <v>2861.1</v>
@@ -2763,28 +2763,28 @@
         <v>1787.2</v>
       </c>
       <c r="M18">
-        <v>129.91484</v>
+        <v>138.0345175</v>
       </c>
       <c r="N18">
-        <v>1657.28516</v>
+        <v>1649.1654825</v>
       </c>
       <c r="O18">
-        <v>364.6027352</v>
+        <v>362.81640615</v>
       </c>
       <c r="P18">
-        <v>1292.6824248</v>
+        <v>1286.34907635</v>
       </c>
       <c r="Q18">
-        <v>2436.3824248</v>
+        <v>2430.04907635</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1065610397832003</v>
+        <v>0.1071528799177547</v>
       </c>
       <c r="T18">
-        <v>0.8363985833738873</v>
+        <v>0.8445454855976036</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.75670400702491</v>
+        <v>12.94748612425874</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09560667033173638</v>
+        <v>0.09542462724558448</v>
       </c>
       <c r="C19">
-        <v>13842.74550712236</v>
+        <v>13708.55650944778</v>
       </c>
       <c r="D19">
-        <v>13725.87050712236</v>
+        <v>13753.10650944778</v>
       </c>
       <c r="E19">
-        <v>-2604.575</v>
+        <v>-2443.15</v>
       </c>
       <c r="F19">
-        <v>2744.225</v>
+        <v>2905.650000000001</v>
       </c>
       <c r="G19">
         <v>2861.1</v>
@@ -2845,28 +2845,28 @@
         <v>1787.2</v>
       </c>
       <c r="M19">
-        <v>138.0345175</v>
+        <v>146.154195</v>
       </c>
       <c r="N19">
-        <v>1649.1654825</v>
+        <v>1641.045805</v>
       </c>
       <c r="O19">
-        <v>362.81640615</v>
+        <v>361.0300771</v>
       </c>
       <c r="P19">
-        <v>1286.34907635</v>
+        <v>1280.0157279</v>
       </c>
       <c r="Q19">
-        <v>2430.04907635</v>
+        <v>2423.7157279</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1071528799177547</v>
+        <v>0.107759155177542</v>
       </c>
       <c r="T19">
-        <v>0.8445454855976036</v>
+        <v>0.8528910927536055</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.94748612425874</v>
+        <v>12.2281813395777</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09542462724558448</v>
+        <v>0.09524258415943256</v>
       </c>
       <c r="C20">
-        <v>13708.55650944778</v>
+        <v>13574.47581451277</v>
       </c>
       <c r="D20">
-        <v>13753.10650944778</v>
+        <v>13780.45081451277</v>
       </c>
       <c r="E20">
-        <v>-2443.15</v>
+        <v>-2281.725</v>
       </c>
       <c r="F20">
-        <v>2905.65</v>
+        <v>3067.075</v>
       </c>
       <c r="G20">
         <v>2861.1</v>
@@ -2927,28 +2927,28 @@
         <v>1787.2</v>
       </c>
       <c r="M20">
-        <v>146.154195</v>
+        <v>154.2738725</v>
       </c>
       <c r="N20">
-        <v>1641.045805</v>
+        <v>1632.9261275</v>
       </c>
       <c r="O20">
-        <v>361.0300771</v>
+        <v>359.24374805</v>
       </c>
       <c r="P20">
-        <v>1280.0157279</v>
+        <v>1273.68237945</v>
       </c>
       <c r="Q20">
-        <v>2423.7157279</v>
+        <v>2417.38237945</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.107759155177542</v>
+        <v>0.1083804001968303</v>
       </c>
       <c r="T20">
-        <v>0.8528910927536053</v>
+        <v>0.8614427642838296</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.2281813395777</v>
+        <v>11.58459284802098</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09524258415943256</v>
+        <v>0.09506054107328067</v>
       </c>
       <c r="C21">
-        <v>13574.47581451277</v>
+        <v>13440.50406959575</v>
       </c>
       <c r="D21">
-        <v>13780.45081451277</v>
+        <v>13807.90406959575</v>
       </c>
       <c r="E21">
-        <v>-2281.725</v>
+        <v>-2120.3</v>
       </c>
       <c r="F21">
-        <v>3067.075</v>
+        <v>3228.5</v>
       </c>
       <c r="G21">
         <v>2861.1</v>
@@ -3009,28 +3009,28 @@
         <v>1787.2</v>
       </c>
       <c r="M21">
-        <v>154.2738725</v>
+        <v>162.39355</v>
       </c>
       <c r="N21">
-        <v>1632.9261275</v>
+        <v>1624.80645</v>
       </c>
       <c r="O21">
-        <v>359.24374805</v>
+        <v>357.457419</v>
       </c>
       <c r="P21">
-        <v>1273.68237945</v>
+        <v>1267.349031</v>
       </c>
       <c r="Q21">
-        <v>2417.38237945</v>
+        <v>2411.049031</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1083804001968303</v>
+        <v>0.1090171763416008</v>
       </c>
       <c r="T21">
-        <v>0.8614427642838296</v>
+        <v>0.8702082276023094</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.58459284802098</v>
+        <v>11.00536320561993</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09506054107328067</v>
+        <v>0.09487849798712877</v>
       </c>
       <c r="C22">
-        <v>13440.50406959575</v>
+        <v>13306.6419271434</v>
       </c>
       <c r="D22">
-        <v>13807.90406959575</v>
+        <v>13835.4669271434</v>
       </c>
       <c r="E22">
-        <v>-2120.3</v>
+        <v>-1958.875</v>
       </c>
       <c r="F22">
-        <v>3228.5</v>
+        <v>3389.925</v>
       </c>
       <c r="G22">
         <v>2861.1</v>
@@ -3091,28 +3091,28 @@
         <v>1787.2</v>
       </c>
       <c r="M22">
-        <v>162.39355</v>
+        <v>170.5132275</v>
       </c>
       <c r="N22">
-        <v>1624.80645</v>
+        <v>1616.6867725</v>
       </c>
       <c r="O22">
-        <v>357.457419</v>
+        <v>355.67108995</v>
       </c>
       <c r="P22">
-        <v>1267.349031</v>
+        <v>1261.01568255</v>
       </c>
       <c r="Q22">
-        <v>2411.049031</v>
+        <v>2404.71568255</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1090171763416008</v>
+        <v>0.1096700734014288</v>
       </c>
       <c r="T22">
-        <v>0.8702082276023094</v>
+        <v>0.8791956013845482</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.00536320561993</v>
+        <v>10.4812982910666</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09487849798712877</v>
+        <v>0.09469645490097686</v>
       </c>
       <c r="C23">
-        <v>13306.6419271434</v>
+        <v>13172.89004482243</v>
       </c>
       <c r="D23">
-        <v>13835.4669271434</v>
+        <v>13863.14004482243</v>
       </c>
       <c r="E23">
-        <v>-1958.875</v>
+        <v>-1797.45</v>
       </c>
       <c r="F23">
-        <v>3389.925</v>
+        <v>3551.35</v>
       </c>
       <c r="G23">
         <v>2861.1</v>
@@ -3173,28 +3173,28 @@
         <v>1787.2</v>
       </c>
       <c r="M23">
-        <v>170.5132275</v>
+        <v>178.632905</v>
       </c>
       <c r="N23">
-        <v>1616.6867725</v>
+        <v>1608.567095</v>
       </c>
       <c r="O23">
-        <v>355.6710899500001</v>
+        <v>353.8847609</v>
       </c>
       <c r="P23">
-        <v>1261.01568255</v>
+        <v>1254.6823341</v>
       </c>
       <c r="Q23">
-        <v>2404.71568255</v>
+        <v>2398.3823341</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1096700734014288</v>
+        <v>0.1103397114115088</v>
       </c>
       <c r="T23">
-        <v>0.8791956013845481</v>
+        <v>0.8884134206483828</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.4812982910666</v>
+        <v>10.00487564147266</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09469645490097686</v>
+        <v>0.09451441181482496</v>
       </c>
       <c r="C24">
-        <v>13172.89004482243</v>
+        <v>13039.24908557182</v>
       </c>
       <c r="D24">
-        <v>13863.14004482243</v>
+        <v>13890.92408557182</v>
       </c>
       <c r="E24">
-        <v>-1797.45</v>
+        <v>-1636.025</v>
       </c>
       <c r="F24">
-        <v>3551.35</v>
+        <v>3712.775</v>
       </c>
       <c r="G24">
         <v>2861.1</v>
@@ -3255,28 +3255,28 @@
         <v>1787.2</v>
       </c>
       <c r="M24">
-        <v>178.632905</v>
+        <v>186.7525825</v>
       </c>
       <c r="N24">
-        <v>1608.567095</v>
+        <v>1600.4474175</v>
       </c>
       <c r="O24">
-        <v>353.8847609</v>
+        <v>352.09843185</v>
       </c>
       <c r="P24">
-        <v>1254.6823341</v>
+        <v>1248.34898565</v>
       </c>
       <c r="Q24">
-        <v>2398.3823341</v>
+        <v>2392.04898565</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1103397114115088</v>
+        <v>0.1110267426166558</v>
       </c>
       <c r="T24">
-        <v>0.8884134206483828</v>
+        <v>0.8978706637892002</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.00487564147266</v>
+        <v>9.569881048365156</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09451441181482496</v>
+        <v>0.09433236872867307</v>
       </c>
       <c r="C25">
-        <v>13039.24908557182</v>
+        <v>12905.71971765577</v>
       </c>
       <c r="D25">
-        <v>13890.92408557182</v>
+        <v>13918.81971765577</v>
       </c>
       <c r="E25">
-        <v>-1636.025</v>
+        <v>-1474.6</v>
       </c>
       <c r="F25">
-        <v>3712.775</v>
+        <v>3874.2</v>
       </c>
       <c r="G25">
         <v>2861.1</v>
@@ -3337,28 +3337,28 @@
         <v>1787.2</v>
       </c>
       <c r="M25">
-        <v>186.7525825</v>
+        <v>194.87226</v>
       </c>
       <c r="N25">
-        <v>1600.4474175</v>
+        <v>1592.32774</v>
       </c>
       <c r="O25">
-        <v>352.09843185</v>
+        <v>350.3121028</v>
       </c>
       <c r="P25">
-        <v>1248.34898565</v>
+        <v>1242.0156372</v>
       </c>
       <c r="Q25">
-        <v>2392.04898565</v>
+        <v>2385.7156372</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1110267426166558</v>
+        <v>0.1117318535903593</v>
       </c>
       <c r="T25">
-        <v>0.8978706637892002</v>
+        <v>0.9075767817495127</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.569881048365156</v>
+        <v>9.171136004683273</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09433236872867307</v>
+        <v>0.09415032564252115</v>
       </c>
       <c r="C26">
-        <v>12905.71971765577</v>
+        <v>12772.30261471732</v>
       </c>
       <c r="D26">
-        <v>13918.81971765577</v>
+        <v>13946.82761471731</v>
       </c>
       <c r="E26">
-        <v>-1474.6</v>
+        <v>-1313.175</v>
       </c>
       <c r="F26">
-        <v>3874.2</v>
+        <v>4035.625</v>
       </c>
       <c r="G26">
         <v>2861.1</v>
@@ -3419,28 +3419,28 @@
         <v>1787.2</v>
       </c>
       <c r="M26">
-        <v>194.87226</v>
+        <v>202.9919375</v>
       </c>
       <c r="N26">
-        <v>1592.32774</v>
+        <v>1584.2080625</v>
       </c>
       <c r="O26">
-        <v>350.3121028</v>
+        <v>348.52577375</v>
       </c>
       <c r="P26">
-        <v>1242.0156372</v>
+        <v>1235.68228875</v>
       </c>
       <c r="Q26">
-        <v>2385.7156372</v>
+        <v>2379.38228875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1117318535903593</v>
+        <v>0.1124557675233615</v>
       </c>
       <c r="T26">
-        <v>0.9075767817495127</v>
+        <v>0.9175417295221002</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.171136004683275</v>
+        <v>8.804290564495943</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09415032564252115</v>
+        <v>0.09427248255636925</v>
       </c>
       <c r="C27">
-        <v>12772.30261471732</v>
+        <v>12592.07096799204</v>
       </c>
       <c r="D27">
-        <v>13946.82761471731</v>
+        <v>13928.02096799204</v>
       </c>
       <c r="E27">
-        <v>-1313.175</v>
+        <v>-1151.75</v>
       </c>
       <c r="F27">
-        <v>4035.625</v>
+        <v>4197.05</v>
       </c>
       <c r="G27">
         <v>2861.1</v>
@@ -3501,45 +3501,45 @@
         <v>1787.2</v>
       </c>
       <c r="M27">
-        <v>202.9919375</v>
+        <v>217.40719</v>
       </c>
       <c r="N27">
-        <v>1584.2080625</v>
+        <v>1569.79281</v>
       </c>
       <c r="O27">
-        <v>348.52577375</v>
+        <v>345.3544182</v>
       </c>
       <c r="P27">
-        <v>1235.68228875</v>
+        <v>1224.4383918</v>
       </c>
       <c r="Q27">
-        <v>2379.38228875</v>
+        <v>2368.1383918</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1124557675233615</v>
+        <v>0.1131992466977963</v>
       </c>
       <c r="T27">
-        <v>0.9175417295221002</v>
+        <v>0.9277760002074605</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>8.804290564495943</v>
+        <v>8.220519293773126</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09427248255636925</v>
+        <v>0.09410213947021735</v>
       </c>
       <c r="C28">
-        <v>12592.07096799204</v>
+        <v>12456.88508437521</v>
       </c>
       <c r="D28">
-        <v>13928.02096799204</v>
+        <v>13954.26008437521</v>
       </c>
       <c r="E28">
-        <v>-1151.75</v>
+        <v>-990.3249999999998</v>
       </c>
       <c r="F28">
-        <v>4197.05</v>
+        <v>4358.475</v>
       </c>
       <c r="G28">
         <v>2861.1</v>
@@ -3583,28 +3583,28 @@
         <v>1787.2</v>
       </c>
       <c r="M28">
-        <v>217.40719</v>
+        <v>225.769005</v>
       </c>
       <c r="N28">
-        <v>1569.79281</v>
+        <v>1561.430995</v>
       </c>
       <c r="O28">
-        <v>345.3544182</v>
+        <v>343.5148189</v>
       </c>
       <c r="P28">
-        <v>1224.4383918</v>
+        <v>1217.9161761</v>
       </c>
       <c r="Q28">
-        <v>2368.1383918</v>
+        <v>2361.6161761</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1131992466977963</v>
+        <v>0.1139630951646813</v>
       </c>
       <c r="T28">
-        <v>0.9277760002074605</v>
+        <v>0.9382906618705017</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.220519293773126</v>
+        <v>7.916055616225973</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09410213947021735</v>
+        <v>0.09393179638406544</v>
       </c>
       <c r="C29">
-        <v>12456.88508437521</v>
+        <v>12321.79825154711</v>
       </c>
       <c r="D29">
-        <v>13954.26008437521</v>
+        <v>13980.59825154711</v>
       </c>
       <c r="E29">
-        <v>-990.3249999999998</v>
+        <v>-828.8999999999996</v>
       </c>
       <c r="F29">
-        <v>4358.475</v>
+        <v>4519.900000000001</v>
       </c>
       <c r="G29">
         <v>2861.1</v>
@@ -3665,28 +3665,28 @@
         <v>1787.2</v>
       </c>
       <c r="M29">
-        <v>225.769005</v>
+        <v>234.13082</v>
       </c>
       <c r="N29">
-        <v>1561.430995</v>
+        <v>1553.06918</v>
       </c>
       <c r="O29">
-        <v>343.5148189</v>
+        <v>341.6752196</v>
       </c>
       <c r="P29">
-        <v>1217.9161761</v>
+        <v>1211.3939604</v>
       </c>
       <c r="Q29">
-        <v>2361.6161761</v>
+        <v>2355.0939604</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1139630951646813</v>
+        <v>0.1147481616445354</v>
       </c>
       <c r="T29">
-        <v>0.9382906618705017</v>
+        <v>0.9490973974686275</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.916055616225973</v>
+        <v>7.633339344217903</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09393179638406544</v>
+        <v>0.09376145329791355</v>
       </c>
       <c r="C30">
-        <v>12321.79825154711</v>
+        <v>12186.81103143282</v>
       </c>
       <c r="D30">
-        <v>13980.59825154711</v>
+        <v>14007.03603143282</v>
       </c>
       <c r="E30">
-        <v>-828.8999999999996</v>
+        <v>-667.4749999999995</v>
       </c>
       <c r="F30">
-        <v>4519.900000000001</v>
+        <v>4681.325000000001</v>
       </c>
       <c r="G30">
         <v>2861.1</v>
@@ -3747,28 +3747,28 @@
         <v>1787.2</v>
       </c>
       <c r="M30">
-        <v>234.13082</v>
+        <v>242.492635</v>
       </c>
       <c r="N30">
-        <v>1553.06918</v>
+        <v>1544.707365</v>
       </c>
       <c r="O30">
-        <v>341.6752196</v>
+        <v>339.8356203</v>
       </c>
       <c r="P30">
-        <v>1211.3939604</v>
+        <v>1204.8717447</v>
       </c>
       <c r="Q30">
-        <v>2355.0939604</v>
+        <v>2348.5717447</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1147481616445354</v>
+        <v>0.1155553426731177</v>
       </c>
       <c r="T30">
-        <v>0.9490973974686275</v>
+        <v>0.9602085481540245</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.633339344217903</v>
+        <v>7.370120746141423</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09376145329791355</v>
+        <v>0.09359111021176164</v>
       </c>
       <c r="C31">
-        <v>12186.81103143282</v>
+        <v>12051.92399021596</v>
       </c>
       <c r="D31">
-        <v>14007.03603143282</v>
+        <v>14033.57399021596</v>
       </c>
       <c r="E31">
-        <v>-667.4750000000004</v>
+        <v>-506.0500000000002</v>
       </c>
       <c r="F31">
-        <v>4681.325</v>
+        <v>4842.75</v>
       </c>
       <c r="G31">
         <v>2861.1</v>
@@ -3829,28 +3829,28 @@
         <v>1787.2</v>
       </c>
       <c r="M31">
-        <v>242.492635</v>
+        <v>250.85445</v>
       </c>
       <c r="N31">
-        <v>1544.707365</v>
+        <v>1536.34555</v>
       </c>
       <c r="O31">
-        <v>339.8356203</v>
+        <v>337.996021</v>
       </c>
       <c r="P31">
-        <v>1204.8717447</v>
+        <v>1198.349529</v>
       </c>
       <c r="Q31">
-        <v>2348.5717447</v>
+        <v>2342.049529</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1155553426731177</v>
+        <v>0.1163855860168024</v>
       </c>
       <c r="T31">
-        <v>0.9602085481540245</v>
+        <v>0.9716371602875755</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.370120746141424</v>
+        <v>7.124450054603377</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09359111021176164</v>
+        <v>0.09342076712560976</v>
       </c>
       <c r="C32">
-        <v>12051.92399021596</v>
+        <v>11917.13769837909</v>
       </c>
       <c r="D32">
-        <v>14033.57399021596</v>
+        <v>14060.21269837909</v>
       </c>
       <c r="E32">
-        <v>-506.0500000000002</v>
+        <v>-344.625</v>
       </c>
       <c r="F32">
-        <v>4842.75</v>
+        <v>5004.175</v>
       </c>
       <c r="G32">
         <v>2861.1</v>
@@ -3911,28 +3911,28 @@
         <v>1787.2</v>
       </c>
       <c r="M32">
-        <v>250.85445</v>
+        <v>259.216265</v>
       </c>
       <c r="N32">
-        <v>1536.34555</v>
+        <v>1527.983735</v>
       </c>
       <c r="O32">
-        <v>337.996021</v>
+        <v>336.1564217</v>
       </c>
       <c r="P32">
-        <v>1198.349529</v>
+        <v>1191.8273133</v>
       </c>
       <c r="Q32">
-        <v>2342.049529</v>
+        <v>2335.5273133</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1163855860168024</v>
+        <v>0.1172398943849417</v>
       </c>
       <c r="T32">
-        <v>0.9716371602875755</v>
+        <v>0.9833970365409398</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.124450054603377</v>
+        <v>6.894629085100042</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09342076712560976</v>
+        <v>0.09367474403945784</v>
       </c>
       <c r="C33">
-        <v>11917.13769837909</v>
+        <v>11716.03201935637</v>
       </c>
       <c r="D33">
-        <v>14060.21269837909</v>
+        <v>14020.53201935637</v>
       </c>
       <c r="E33">
-        <v>-344.625</v>
+        <v>-183.1999999999998</v>
       </c>
       <c r="F33">
-        <v>5004.175</v>
+        <v>5165.6</v>
       </c>
       <c r="G33">
         <v>2861.1</v>
@@ -3993,45 +3993,45 @@
         <v>1787.2</v>
       </c>
       <c r="M33">
-        <v>259.216265</v>
+        <v>276.3596</v>
       </c>
       <c r="N33">
-        <v>1527.983735</v>
+        <v>1510.8404</v>
       </c>
       <c r="O33">
-        <v>336.1564217</v>
+        <v>332.384888</v>
       </c>
       <c r="P33">
-        <v>1191.8273133</v>
+        <v>1178.455512</v>
       </c>
       <c r="Q33">
-        <v>2335.5273133</v>
+        <v>2322.155512</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1172398943849417</v>
+        <v>0.118119329469791</v>
       </c>
       <c r="T33">
-        <v>0.9833970365409398</v>
+        <v>0.9955027915076382</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.894629085100042</v>
+        <v>6.466936556573392</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09367474403945784</v>
+        <v>0.09351766095330594</v>
       </c>
       <c r="C34">
-        <v>11716.03201935637</v>
+        <v>11579.12279337781</v>
       </c>
       <c r="D34">
-        <v>14020.53201935637</v>
+        <v>14045.04779337781</v>
       </c>
       <c r="E34">
-        <v>-183.1999999999998</v>
+        <v>-21.77499999999964</v>
       </c>
       <c r="F34">
-        <v>5165.6</v>
+        <v>5327.025000000001</v>
       </c>
       <c r="G34">
         <v>2861.1</v>
@@ -4075,28 +4075,28 @@
         <v>1787.2</v>
       </c>
       <c r="M34">
-        <v>276.3596</v>
+        <v>284.9958375000001</v>
       </c>
       <c r="N34">
-        <v>1510.8404</v>
+        <v>1502.2041625</v>
       </c>
       <c r="O34">
-        <v>332.384888</v>
+        <v>330.48491575</v>
       </c>
       <c r="P34">
-        <v>1178.455512</v>
+        <v>1171.71924675</v>
       </c>
       <c r="Q34">
-        <v>2322.155512</v>
+        <v>2315.41924675</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.118119329469791</v>
+        <v>0.1190250163482178</v>
       </c>
       <c r="T34">
-        <v>0.9955027915076382</v>
+        <v>1.007969912294238</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.466936556573392</v>
+        <v>6.270968782131773</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09351766095330594</v>
+        <v>0.09336057786715404</v>
       </c>
       <c r="C35">
-        <v>11579.12279337781</v>
+        <v>11442.29945229182</v>
       </c>
       <c r="D35">
-        <v>14045.04779337781</v>
+        <v>14069.64945229183</v>
       </c>
       <c r="E35">
-        <v>-21.77499999999964</v>
+        <v>139.6500000000005</v>
       </c>
       <c r="F35">
-        <v>5327.025000000001</v>
+        <v>5488.450000000001</v>
       </c>
       <c r="G35">
         <v>2861.1</v>
@@ -4157,28 +4157,28 @@
         <v>1787.2</v>
       </c>
       <c r="M35">
-        <v>284.9958375000001</v>
+        <v>293.632075</v>
       </c>
       <c r="N35">
-        <v>1502.2041625</v>
+        <v>1493.567925</v>
       </c>
       <c r="O35">
-        <v>330.48491575</v>
+        <v>328.5849435</v>
       </c>
       <c r="P35">
-        <v>1171.71924675</v>
+        <v>1164.9829815</v>
       </c>
       <c r="Q35">
-        <v>2315.41924675</v>
+        <v>2308.6829815</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1190250163482178</v>
+        <v>0.1199581482835667</v>
       </c>
       <c r="T35">
-        <v>1.007969912294238</v>
+        <v>1.020814824619826</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.270968782131773</v>
+        <v>6.08652852383378</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09336057786715404</v>
+        <v>0.09320349478100215</v>
       </c>
       <c r="C36">
-        <v>11442.29945229182</v>
+        <v>11305.56244820475</v>
       </c>
       <c r="D36">
-        <v>14069.64945229183</v>
+        <v>14094.33744820475</v>
       </c>
       <c r="E36">
-        <v>139.6500000000005</v>
+        <v>301.0750000000007</v>
       </c>
       <c r="F36">
-        <v>5488.450000000001</v>
+        <v>5649.875000000001</v>
       </c>
       <c r="G36">
         <v>2861.1</v>
@@ -4239,28 +4239,28 @@
         <v>1787.2</v>
       </c>
       <c r="M36">
-        <v>293.632075</v>
+        <v>302.2683125</v>
       </c>
       <c r="N36">
-        <v>1493.567925</v>
+        <v>1484.9316875</v>
       </c>
       <c r="O36">
-        <v>328.5849435</v>
+        <v>326.68497125</v>
       </c>
       <c r="P36">
-        <v>1164.9829815</v>
+        <v>1158.24671625</v>
       </c>
       <c r="Q36">
-        <v>2308.6829815</v>
+        <v>2301.94671625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1199581482835667</v>
+        <v>0.1209199919707726</v>
       </c>
       <c r="T36">
-        <v>1.020814824619826</v>
+        <v>1.03405496501697</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.08652852383378</v>
+        <v>5.912627708867101</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09320349478100215</v>
+        <v>0.09304641169485026</v>
       </c>
       <c r="C37">
-        <v>11305.56244820475</v>
+        <v>11168.91223640174</v>
       </c>
       <c r="D37">
-        <v>14094.33744820475</v>
+        <v>14119.11223640174</v>
       </c>
       <c r="E37">
-        <v>301.0750000000007</v>
+        <v>462.5000000000009</v>
       </c>
       <c r="F37">
-        <v>5649.875000000001</v>
+        <v>5811.300000000001</v>
       </c>
       <c r="G37">
         <v>2861.1</v>
@@ -4321,28 +4321,28 @@
         <v>1787.2</v>
       </c>
       <c r="M37">
-        <v>302.2683125</v>
+        <v>310.90455</v>
       </c>
       <c r="N37">
-        <v>1484.9316875</v>
+        <v>1476.29545</v>
       </c>
       <c r="O37">
-        <v>326.68497125</v>
+        <v>324.784999</v>
       </c>
       <c r="P37">
-        <v>1158.24671625</v>
+        <v>1151.510451</v>
       </c>
       <c r="Q37">
-        <v>2301.94671625</v>
+        <v>2295.210451</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1209199919707726</v>
+        <v>0.1219118932732035</v>
       </c>
       <c r="T37">
-        <v>1.03405496501697</v>
+        <v>1.047708859801525</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.912627708867101</v>
+        <v>5.74838805028746</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09304641169485026</v>
+        <v>0.09288932860869833</v>
       </c>
       <c r="C38">
-        <v>11168.91223640175</v>
+        <v>11032.34927537476</v>
       </c>
       <c r="D38">
-        <v>14119.11223640174</v>
+        <v>14143.97427537476</v>
       </c>
       <c r="E38">
-        <v>462.5</v>
+        <v>623.9250000000002</v>
       </c>
       <c r="F38">
-        <v>5811.3</v>
+        <v>5972.725</v>
       </c>
       <c r="G38">
         <v>2861.1</v>
@@ -4403,28 +4403,28 @@
         <v>1787.2</v>
       </c>
       <c r="M38">
-        <v>310.90455</v>
+        <v>319.5407875</v>
       </c>
       <c r="N38">
-        <v>1476.29545</v>
+        <v>1467.6592125</v>
       </c>
       <c r="O38">
-        <v>324.784999</v>
+        <v>322.88502675</v>
       </c>
       <c r="P38">
-        <v>1151.510451</v>
+        <v>1144.77418575</v>
       </c>
       <c r="Q38">
-        <v>2295.210451</v>
+        <v>2288.47418575</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1219118932732035</v>
+        <v>0.1229352835058704</v>
       </c>
       <c r="T38">
-        <v>1.047708859801525</v>
+        <v>1.061796211563368</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.74838805028746</v>
+        <v>5.593026211090501</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09288932860869833</v>
+        <v>0.09296936552254643</v>
       </c>
       <c r="C39">
-        <v>11032.34927537476</v>
+        <v>10858.24564782473</v>
       </c>
       <c r="D39">
-        <v>14143.97427537476</v>
+        <v>14131.29564782473</v>
       </c>
       <c r="E39">
-        <v>623.9250000000002</v>
+        <v>785.3499999999995</v>
       </c>
       <c r="F39">
-        <v>5972.725</v>
+        <v>6134.15</v>
       </c>
       <c r="G39">
         <v>2861.1</v>
@@ -4485,45 +4485,45 @@
         <v>1787.2</v>
       </c>
       <c r="M39">
-        <v>319.5407875</v>
+        <v>333.084345</v>
       </c>
       <c r="N39">
-        <v>1467.6592125</v>
+        <v>1454.115655</v>
       </c>
       <c r="O39">
-        <v>322.88502675</v>
+        <v>319.9054441</v>
       </c>
       <c r="P39">
-        <v>1144.77418575</v>
+        <v>1134.2102109</v>
       </c>
       <c r="Q39">
-        <v>2288.47418575</v>
+        <v>2277.9102109</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1229352835058704</v>
+        <v>0.1239916863266878</v>
       </c>
       <c r="T39">
-        <v>1.061796211563368</v>
+        <v>1.076337994027205</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>5.593026211090501</v>
+        <v>5.36560792132095</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09296936552254643</v>
+        <v>0.09281852243639455</v>
       </c>
       <c r="C40">
-        <v>10858.24564782473</v>
+        <v>10720.73464464041</v>
       </c>
       <c r="D40">
-        <v>14131.29564782473</v>
+        <v>14155.20964464041</v>
       </c>
       <c r="E40">
-        <v>785.3499999999995</v>
+        <v>946.7749999999996</v>
       </c>
       <c r="F40">
-        <v>6134.15</v>
+        <v>6295.575</v>
       </c>
       <c r="G40">
         <v>2861.1</v>
@@ -4567,28 +4567,28 @@
         <v>1787.2</v>
       </c>
       <c r="M40">
-        <v>333.084345</v>
+        <v>341.8497225</v>
       </c>
       <c r="N40">
-        <v>1454.115655</v>
+        <v>1445.3502775</v>
       </c>
       <c r="O40">
-        <v>319.9054441</v>
+        <v>317.97706105</v>
       </c>
       <c r="P40">
-        <v>1134.2102109</v>
+        <v>1127.37321645</v>
       </c>
       <c r="Q40">
-        <v>2277.9102109</v>
+        <v>2271.07321645</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1239916863266878</v>
+        <v>0.1250827253055648</v>
       </c>
       <c r="T40">
-        <v>1.076337994027205</v>
+        <v>1.091356556243955</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.36560792132095</v>
+        <v>5.228028231030669</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09281852243639455</v>
+        <v>0.09266767935024266</v>
       </c>
       <c r="C41">
-        <v>10720.73464464041</v>
+        <v>10583.30471663473</v>
       </c>
       <c r="D41">
-        <v>14155.20964464041</v>
+        <v>14179.20471663473</v>
       </c>
       <c r="E41">
-        <v>946.7749999999996</v>
+        <v>1108.2</v>
       </c>
       <c r="F41">
-        <v>6295.575</v>
+        <v>6457</v>
       </c>
       <c r="G41">
         <v>2861.1</v>
@@ -4649,28 +4649,28 @@
         <v>1787.2</v>
       </c>
       <c r="M41">
-        <v>341.8497225</v>
+        <v>350.6151</v>
       </c>
       <c r="N41">
-        <v>1445.3502775</v>
+        <v>1436.5849</v>
       </c>
       <c r="O41">
-        <v>317.97706105</v>
+        <v>316.048678</v>
       </c>
       <c r="P41">
-        <v>1127.37321645</v>
+        <v>1120.536222</v>
       </c>
       <c r="Q41">
-        <v>2271.07321645</v>
+        <v>2264.236222</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1250827253055648</v>
+        <v>0.1262101322504044</v>
       </c>
       <c r="T41">
-        <v>1.091356556243955</v>
+        <v>1.106875737201264</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.228028231030669</v>
+        <v>5.097327525254903</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09266767935024266</v>
+        <v>0.09251683626409073</v>
       </c>
       <c r="C42">
-        <v>10583.30471663473</v>
+        <v>10445.95627680928</v>
       </c>
       <c r="D42">
-        <v>14179.20471663473</v>
+        <v>14203.28127680928</v>
       </c>
       <c r="E42">
-        <v>1108.2</v>
+        <v>1269.625</v>
       </c>
       <c r="F42">
-        <v>6457</v>
+        <v>6618.425</v>
       </c>
       <c r="G42">
         <v>2861.1</v>
@@ -4731,28 +4731,28 @@
         <v>1787.2</v>
       </c>
       <c r="M42">
-        <v>350.6151</v>
+        <v>359.3804775</v>
       </c>
       <c r="N42">
-        <v>1436.5849</v>
+        <v>1427.8195225</v>
       </c>
       <c r="O42">
-        <v>316.048678</v>
+        <v>314.12029495</v>
       </c>
       <c r="P42">
-        <v>1120.536222</v>
+        <v>1113.69922755</v>
       </c>
       <c r="Q42">
-        <v>2264.236222</v>
+        <v>2257.39922755</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1262101322504044</v>
+        <v>0.1273757563798148</v>
       </c>
       <c r="T42">
-        <v>1.106875737201264</v>
+        <v>1.122920992089328</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.097327525254903</v>
+        <v>4.973002463663319</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09251683626409073</v>
+        <v>0.09236599317793882</v>
       </c>
       <c r="C43">
-        <v>10445.95627680928</v>
+        <v>10308.68974097557</v>
       </c>
       <c r="D43">
-        <v>14203.28127680928</v>
+        <v>14227.43974097557</v>
       </c>
       <c r="E43">
-        <v>1269.625</v>
+        <v>1431.05</v>
       </c>
       <c r="F43">
-        <v>6618.425</v>
+        <v>6779.85</v>
       </c>
       <c r="G43">
         <v>2861.1</v>
@@ -4813,28 +4813,28 @@
         <v>1787.2</v>
       </c>
       <c r="M43">
-        <v>359.3804775</v>
+        <v>368.145855</v>
       </c>
       <c r="N43">
-        <v>1427.8195225</v>
+        <v>1419.054145</v>
       </c>
       <c r="O43">
-        <v>314.12029495</v>
+        <v>312.1919119</v>
       </c>
       <c r="P43">
-        <v>1113.69922755</v>
+        <v>1106.8622331</v>
       </c>
       <c r="Q43">
-        <v>2257.39922755</v>
+        <v>2250.5622331</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1273757563798148</v>
+        <v>0.1285815744447221</v>
       </c>
       <c r="T43">
-        <v>1.122920992089328</v>
+        <v>1.139519531628706</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.973002463663319</v>
+        <v>4.854597643099906</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09236599317793884</v>
+        <v>0.09221515009178695</v>
       </c>
       <c r="C44">
-        <v>10308.68974097557</v>
+        <v>10171.50552777897</v>
       </c>
       <c r="D44">
-        <v>14227.43974097557</v>
+        <v>14251.68052777897</v>
       </c>
       <c r="E44">
-        <v>1431.049999999999</v>
+        <v>1592.474999999999</v>
       </c>
       <c r="F44">
-        <v>6779.849999999999</v>
+        <v>6941.275</v>
       </c>
       <c r="G44">
         <v>2861.1</v>
@@ -4895,28 +4895,28 @@
         <v>1787.2</v>
       </c>
       <c r="M44">
-        <v>368.145855</v>
+        <v>376.9112325</v>
       </c>
       <c r="N44">
-        <v>1419.054145</v>
+        <v>1410.2887675</v>
       </c>
       <c r="O44">
-        <v>312.1919119</v>
+        <v>310.2635288500001</v>
       </c>
       <c r="P44">
-        <v>1106.8622331</v>
+        <v>1100.02523865</v>
       </c>
       <c r="Q44">
-        <v>2250.5622331</v>
+        <v>2243.72523865</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1285815744447221</v>
+        <v>0.1298297019154157</v>
       </c>
       <c r="T44">
-        <v>1.139519531628706</v>
+        <v>1.156700476064201</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.854597643099908</v>
+        <v>4.741700023492933</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09221515009178695</v>
+        <v>0.09206430700563505</v>
       </c>
       <c r="C45">
-        <v>10171.50552777897</v>
+        <v>10034.40405872286</v>
       </c>
       <c r="D45">
-        <v>14251.68052777897</v>
+        <v>14276.00405872286</v>
       </c>
       <c r="E45">
-        <v>1592.474999999999</v>
+        <v>1753.9</v>
       </c>
       <c r="F45">
-        <v>6941.275</v>
+        <v>7102.7</v>
       </c>
       <c r="G45">
         <v>2861.1</v>
@@ -4977,28 +4977,28 @@
         <v>1787.2</v>
       </c>
       <c r="M45">
-        <v>376.9112325</v>
+        <v>385.67661</v>
       </c>
       <c r="N45">
-        <v>1410.2887675</v>
+        <v>1401.52339</v>
       </c>
       <c r="O45">
-        <v>310.2635288500001</v>
+        <v>308.3351458</v>
       </c>
       <c r="P45">
-        <v>1100.02523865</v>
+        <v>1093.1882442</v>
       </c>
       <c r="Q45">
-        <v>2243.72523865</v>
+        <v>2236.8882442</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1298297019154157</v>
+        <v>0.1311224053672054</v>
       </c>
       <c r="T45">
-        <v>1.156700476064201</v>
+        <v>1.174495025658108</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.741700023492933</v>
+        <v>4.633934113868094</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09206430700563505</v>
+        <v>0.09191346391948313</v>
       </c>
       <c r="C46">
-        <v>10034.40405872286</v>
+        <v>9897.38575819309</v>
       </c>
       <c r="D46">
-        <v>14276.00405872286</v>
+        <v>14300.41075819309</v>
       </c>
       <c r="E46">
-        <v>1753.9</v>
+        <v>1915.325</v>
       </c>
       <c r="F46">
-        <v>7102.7</v>
+        <v>7264.125</v>
       </c>
       <c r="G46">
         <v>2861.1</v>
@@ -5059,28 +5059,28 @@
         <v>1787.2</v>
       </c>
       <c r="M46">
-        <v>385.67661</v>
+        <v>394.4419875</v>
       </c>
       <c r="N46">
-        <v>1401.52339</v>
+        <v>1392.7580125</v>
       </c>
       <c r="O46">
-        <v>308.3351458</v>
+        <v>306.40676275</v>
       </c>
       <c r="P46">
-        <v>1093.1882442</v>
+        <v>1086.35124975</v>
       </c>
       <c r="Q46">
-        <v>2236.8882442</v>
+        <v>2230.05124975</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1311224053672054</v>
+        <v>0.132462116217242</v>
       </c>
       <c r="T46">
-        <v>1.174495025658108</v>
+        <v>1.192936649782702</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.633934113868094</v>
+        <v>4.530957800226579</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09191346391948313</v>
+        <v>0.09176262083333125</v>
       </c>
       <c r="C47">
-        <v>9897.38575819309</v>
+        <v>9760.451053482651</v>
       </c>
       <c r="D47">
-        <v>14300.41075819309</v>
+        <v>14324.90105348265</v>
       </c>
       <c r="E47">
-        <v>1915.325</v>
+        <v>2076.75</v>
       </c>
       <c r="F47">
-        <v>7264.125</v>
+        <v>7425.55</v>
       </c>
       <c r="G47">
         <v>2861.1</v>
@@ -5141,28 +5141,28 @@
         <v>1787.2</v>
       </c>
       <c r="M47">
-        <v>394.4419875</v>
+        <v>403.207365</v>
       </c>
       <c r="N47">
-        <v>1392.7580125</v>
+        <v>1383.992635</v>
       </c>
       <c r="O47">
-        <v>306.40676275</v>
+        <v>304.4783797</v>
       </c>
       <c r="P47">
-        <v>1086.35124975</v>
+        <v>1079.5142553</v>
       </c>
       <c r="Q47">
-        <v>2230.05124975</v>
+        <v>2223.2142553</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.132462116217242</v>
+        <v>0.1338514459876504</v>
       </c>
       <c r="T47">
-        <v>1.192936649782702</v>
+        <v>1.212061297023021</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.530957800226579</v>
+        <v>4.432458717612958</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09176262083333125</v>
+        <v>0.09161177774717935</v>
       </c>
       <c r="C48">
-        <v>9760.451053482651</v>
+        <v>9623.60037481662</v>
       </c>
       <c r="D48">
-        <v>14324.90105348265</v>
+        <v>14349.47537481662</v>
       </c>
       <c r="E48">
-        <v>2076.75</v>
+        <v>2238.175</v>
       </c>
       <c r="F48">
-        <v>7425.55</v>
+        <v>7586.975</v>
       </c>
       <c r="G48">
         <v>2861.1</v>
@@ -5223,28 +5223,28 @@
         <v>1787.2</v>
       </c>
       <c r="M48">
-        <v>403.207365</v>
+        <v>411.9727425</v>
       </c>
       <c r="N48">
-        <v>1383.992635</v>
+        <v>1375.2272575</v>
       </c>
       <c r="O48">
-        <v>304.4783797</v>
+        <v>302.54999665</v>
       </c>
       <c r="P48">
-        <v>1079.5142553</v>
+        <v>1072.67726085</v>
       </c>
       <c r="Q48">
-        <v>2223.2142553</v>
+        <v>2216.37726085</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1338514459876504</v>
+        <v>0.1352932032965648</v>
       </c>
       <c r="T48">
-        <v>1.212061297023021</v>
+        <v>1.231907629064863</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.432458717612958</v>
+        <v>4.33815108532332</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09161177774717935</v>
+        <v>0.09183533466102745</v>
       </c>
       <c r="C49">
-        <v>9623.60037481662</v>
+        <v>9425.785056832738</v>
       </c>
       <c r="D49">
-        <v>14349.47537481662</v>
+        <v>14313.08505683274</v>
       </c>
       <c r="E49">
-        <v>2238.175</v>
+        <v>2399.6</v>
       </c>
       <c r="F49">
-        <v>7586.975</v>
+        <v>7748.400000000001</v>
       </c>
       <c r="G49">
         <v>2861.1</v>
@@ -5305,45 +5305,45 @@
         <v>1787.2</v>
       </c>
       <c r="M49">
-        <v>411.9727425</v>
+        <v>428.48652</v>
       </c>
       <c r="N49">
-        <v>1375.2272575</v>
+        <v>1358.71348</v>
       </c>
       <c r="O49">
-        <v>302.54999665</v>
+        <v>298.9169656</v>
       </c>
       <c r="P49">
-        <v>1072.67726085</v>
+        <v>1059.7965144</v>
       </c>
       <c r="Q49">
-        <v>2216.37726085</v>
+        <v>2203.4965144</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1352932032965648</v>
+        <v>0.1367904128096682</v>
       </c>
       <c r="T49">
-        <v>1.231907629064863</v>
+        <v>1.252517281569851</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.22</v>
       </c>
       <c r="W49">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.33815108532332</v>
+        <v>4.170959683865901</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09183533466102743</v>
+        <v>0.09169229157487553</v>
       </c>
       <c r="C50">
-        <v>9425.785056832743</v>
+        <v>9287.62313240501</v>
       </c>
       <c r="D50">
-        <v>14313.08505683274</v>
+        <v>14336.34813240501</v>
       </c>
       <c r="E50">
-        <v>2399.599999999999</v>
+        <v>2561.025</v>
       </c>
       <c r="F50">
-        <v>7748.4</v>
+        <v>7909.825</v>
       </c>
       <c r="G50">
         <v>2861.1</v>
@@ -5387,28 +5387,28 @@
         <v>1787.2</v>
       </c>
       <c r="M50">
-        <v>428.48652</v>
+        <v>437.4133225</v>
       </c>
       <c r="N50">
-        <v>1358.71348</v>
+        <v>1349.7866775</v>
       </c>
       <c r="O50">
-        <v>298.9169656</v>
+        <v>296.95306905</v>
       </c>
       <c r="P50">
-        <v>1059.7965144</v>
+        <v>1052.83360845</v>
       </c>
       <c r="Q50">
-        <v>2203.4965144</v>
+        <v>2196.53360845</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1367904128096681</v>
+        <v>0.1383463364213246</v>
       </c>
       <c r="T50">
-        <v>1.252517281569851</v>
+        <v>1.273935155741702</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.170959683865901</v>
+        <v>4.085838057664557</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09169229157487553</v>
+        <v>0.09154924848872363</v>
       </c>
       <c r="C51">
-        <v>9287.62313240501</v>
+        <v>9149.536950094403</v>
       </c>
       <c r="D51">
-        <v>14336.34813240501</v>
+        <v>14359.6869500944</v>
       </c>
       <c r="E51">
-        <v>2561.025</v>
+        <v>2722.45</v>
       </c>
       <c r="F51">
-        <v>7909.825</v>
+        <v>8071.25</v>
       </c>
       <c r="G51">
         <v>2861.1</v>
@@ -5469,28 +5469,28 @@
         <v>1787.2</v>
       </c>
       <c r="M51">
-        <v>437.4133225</v>
+        <v>446.340125</v>
       </c>
       <c r="N51">
-        <v>1349.7866775</v>
+        <v>1340.859875</v>
       </c>
       <c r="O51">
-        <v>296.95306905</v>
+        <v>294.9891725000001</v>
       </c>
       <c r="P51">
-        <v>1052.83360845</v>
+        <v>1045.8707025</v>
       </c>
       <c r="Q51">
-        <v>2196.53360845</v>
+        <v>2189.5707025</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1383463364213246</v>
+        <v>0.1399644969774473</v>
       </c>
       <c r="T51">
-        <v>1.273935155741702</v>
+        <v>1.296209744880427</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.085838057664557</v>
+        <v>4.004121296511265</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09154924848872363</v>
+        <v>0.09140620540257173</v>
       </c>
       <c r="C52">
-        <v>9149.536950094403</v>
+        <v>9011.526880416597</v>
       </c>
       <c r="D52">
-        <v>14359.6869500944</v>
+        <v>14383.1018804166</v>
       </c>
       <c r="E52">
-        <v>2722.45</v>
+        <v>2883.874999999999</v>
       </c>
       <c r="F52">
-        <v>8071.25</v>
+        <v>8232.674999999999</v>
       </c>
       <c r="G52">
         <v>2861.1</v>
@@ -5551,28 +5551,28 @@
         <v>1787.2</v>
       </c>
       <c r="M52">
-        <v>446.340125</v>
+        <v>455.2669275</v>
       </c>
       <c r="N52">
-        <v>1340.859875</v>
+        <v>1331.9330725</v>
       </c>
       <c r="O52">
-        <v>294.9891725000001</v>
+        <v>293.02527595</v>
       </c>
       <c r="P52">
-        <v>1045.8707025</v>
+        <v>1038.90779655</v>
       </c>
       <c r="Q52">
-        <v>2189.5707025</v>
+        <v>2182.60779655</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1399644969774473</v>
+        <v>0.1416487049032076</v>
       </c>
       <c r="T52">
-        <v>1.296209744880427</v>
+        <v>1.319393500922774</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.004121296511265</v>
+        <v>3.92560911422673</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09140620540257173</v>
+        <v>0.09126316231641984</v>
       </c>
       <c r="C53">
-        <v>9011.526880416597</v>
+        <v>8873.593296307872</v>
       </c>
       <c r="D53">
-        <v>14383.1018804166</v>
+        <v>14406.59329630787</v>
       </c>
       <c r="E53">
-        <v>2883.874999999999</v>
+        <v>3045.3</v>
       </c>
       <c r="F53">
-        <v>8232.674999999999</v>
+        <v>8394.1</v>
       </c>
       <c r="G53">
         <v>2861.1</v>
@@ -5633,28 +5633,28 @@
         <v>1787.2</v>
       </c>
       <c r="M53">
-        <v>455.2669275</v>
+        <v>464.19373</v>
       </c>
       <c r="N53">
-        <v>1331.9330725</v>
+        <v>1323.00627</v>
       </c>
       <c r="O53">
-        <v>293.02527595</v>
+        <v>291.0613794</v>
       </c>
       <c r="P53">
-        <v>1038.90779655</v>
+        <v>1031.9448906</v>
       </c>
       <c r="Q53">
-        <v>2182.60779655</v>
+        <v>2175.6448906</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1416487049032076</v>
+        <v>0.143403088159208</v>
       </c>
       <c r="T53">
-        <v>1.319393500922774</v>
+        <v>1.343543246800218</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.92560911422673</v>
+        <v>3.850116631260831</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09126316231641984</v>
+        <v>0.09112011923026792</v>
       </c>
       <c r="C54">
-        <v>8873.593296307872</v>
+        <v>8735.736573144926</v>
       </c>
       <c r="D54">
-        <v>14406.59329630787</v>
+        <v>14430.16157314493</v>
       </c>
       <c r="E54">
-        <v>3045.3</v>
+        <v>3206.724999999999</v>
       </c>
       <c r="F54">
-        <v>8394.1</v>
+        <v>8555.525</v>
       </c>
       <c r="G54">
         <v>2861.1</v>
@@ -5715,28 +5715,28 @@
         <v>1787.2</v>
       </c>
       <c r="M54">
-        <v>464.19373</v>
+        <v>473.1205325</v>
       </c>
       <c r="N54">
-        <v>1323.00627</v>
+        <v>1314.0794675</v>
       </c>
       <c r="O54">
-        <v>291.0613794</v>
+        <v>289.09748285</v>
       </c>
       <c r="P54">
-        <v>1031.9448906</v>
+        <v>1024.98198465</v>
       </c>
       <c r="Q54">
-        <v>2175.6448906</v>
+        <v>2168.68198465</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.143403088159208</v>
+        <v>0.1452321260218467</v>
       </c>
       <c r="T54">
-        <v>1.343543246800218</v>
+        <v>1.368720641438405</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.850116631260831</v>
+        <v>3.777472921237042</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09112011923026792</v>
+        <v>0.09097707614411601</v>
       </c>
       <c r="C55">
-        <v>8735.736573144926</v>
+        <v>8597.957088764819</v>
       </c>
       <c r="D55">
-        <v>14430.16157314493</v>
+        <v>14453.80708876482</v>
       </c>
       <c r="E55">
-        <v>3206.724999999999</v>
+        <v>3368.150000000001</v>
       </c>
       <c r="F55">
-        <v>8555.525</v>
+        <v>8716.950000000001</v>
       </c>
       <c r="G55">
         <v>2861.1</v>
@@ -5797,28 +5797,28 @@
         <v>1787.2</v>
       </c>
       <c r="M55">
-        <v>473.1205325</v>
+        <v>482.047335</v>
       </c>
       <c r="N55">
-        <v>1314.0794675</v>
+        <v>1305.152665</v>
       </c>
       <c r="O55">
-        <v>289.09748285</v>
+        <v>287.1335863</v>
       </c>
       <c r="P55">
-        <v>1024.98198465</v>
+        <v>1018.0190787</v>
       </c>
       <c r="Q55">
-        <v>2168.68198465</v>
+        <v>2161.7190787</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1452321260218467</v>
+        <v>0.1471406872698174</v>
       </c>
       <c r="T55">
-        <v>1.368720641438405</v>
+        <v>1.394992705408687</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.777472921237042</v>
+        <v>3.707519718991912</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09097707614411601</v>
+        <v>0.09083403305796413</v>
       </c>
       <c r="C56">
-        <v>8597.957088764819</v>
+        <v>8460.255223485219</v>
       </c>
       <c r="D56">
-        <v>14453.80708876482</v>
+        <v>14477.53022348522</v>
       </c>
       <c r="E56">
-        <v>3368.150000000001</v>
+        <v>3529.575</v>
       </c>
       <c r="F56">
-        <v>8716.950000000001</v>
+        <v>8878.375</v>
       </c>
       <c r="G56">
         <v>2861.1</v>
@@ -5879,28 +5879,28 @@
         <v>1787.2</v>
       </c>
       <c r="M56">
-        <v>482.047335</v>
+        <v>490.9741375</v>
       </c>
       <c r="N56">
-        <v>1305.152665</v>
+        <v>1296.2258625</v>
       </c>
       <c r="O56">
-        <v>287.1335863</v>
+        <v>285.16968975</v>
       </c>
       <c r="P56">
-        <v>1018.0190787</v>
+        <v>1011.05617275</v>
       </c>
       <c r="Q56">
-        <v>2161.7190787</v>
+        <v>2154.75617275</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1471406872698174</v>
+        <v>0.1491340734621425</v>
       </c>
       <c r="T56">
-        <v>1.394992705408687</v>
+        <v>1.422432416666537</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.707519718991912</v>
+        <v>3.640110269555695</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09083403305796413</v>
+        <v>0.09069098997181223</v>
       </c>
       <c r="C57">
-        <v>8460.255223485219</v>
+        <v>8322.631360124769</v>
       </c>
       <c r="D57">
-        <v>14477.53022348522</v>
+        <v>14501.33136012477</v>
       </c>
       <c r="E57">
-        <v>3529.575</v>
+        <v>3691.000000000001</v>
       </c>
       <c r="F57">
-        <v>8878.375</v>
+        <v>9039.800000000001</v>
       </c>
       <c r="G57">
         <v>2861.1</v>
@@ -5961,28 +5961,28 @@
         <v>1787.2</v>
       </c>
       <c r="M57">
-        <v>490.9741375</v>
+        <v>499.9009400000001</v>
       </c>
       <c r="N57">
-        <v>1296.2258625</v>
+        <v>1287.29906</v>
       </c>
       <c r="O57">
-        <v>285.16968975</v>
+        <v>283.2057932</v>
       </c>
       <c r="P57">
-        <v>1011.05617275</v>
+        <v>1004.0932668</v>
       </c>
       <c r="Q57">
-        <v>2154.75617275</v>
+        <v>2147.7932668</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1491340734621425</v>
+        <v>0.1512180681177551</v>
       </c>
       <c r="T57">
-        <v>1.422432416666537</v>
+        <v>1.451119387527016</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.640110269555695</v>
+        <v>3.575108300456486</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09069098997181223</v>
+        <v>0.09054794688566033</v>
       </c>
       <c r="C58">
-        <v>8322.631360124769</v>
+        <v>8185.085884023685</v>
       </c>
       <c r="D58">
-        <v>14501.33136012477</v>
+        <v>14525.21088402369</v>
       </c>
       <c r="E58">
-        <v>3691.000000000001</v>
+        <v>3852.425</v>
       </c>
       <c r="F58">
-        <v>9039.800000000001</v>
+        <v>9201.225</v>
       </c>
       <c r="G58">
         <v>2861.1</v>
@@ -6043,28 +6043,28 @@
         <v>1787.2</v>
       </c>
       <c r="M58">
-        <v>499.9009400000001</v>
+        <v>508.8277425000001</v>
       </c>
       <c r="N58">
-        <v>1287.29906</v>
+        <v>1278.3722575</v>
       </c>
       <c r="O58">
-        <v>283.2057932</v>
+        <v>281.24189665</v>
       </c>
       <c r="P58">
-        <v>1004.0932668</v>
+        <v>997.13036085</v>
       </c>
       <c r="Q58">
-        <v>2147.7932668</v>
+        <v>2140.83036085</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1512180681177551</v>
+        <v>0.1533989927573496</v>
       </c>
       <c r="T58">
-        <v>1.451119387527016</v>
+        <v>1.481140636101936</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.575108300456486</v>
+        <v>3.512387102202863</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09054794688566033</v>
+        <v>0.09040490379950843</v>
       </c>
       <c r="C59">
-        <v>8185.085884023685</v>
+        <v>8047.619183064533</v>
       </c>
       <c r="D59">
-        <v>14525.21088402369</v>
+        <v>14549.16918306453</v>
       </c>
       <c r="E59">
-        <v>3852.425</v>
+        <v>4013.850000000001</v>
       </c>
       <c r="F59">
-        <v>9201.225</v>
+        <v>9362.650000000001</v>
       </c>
       <c r="G59">
         <v>2861.1</v>
@@ -6125,28 +6125,28 @@
         <v>1787.2</v>
       </c>
       <c r="M59">
-        <v>508.8277425000001</v>
+        <v>517.7545450000001</v>
       </c>
       <c r="N59">
-        <v>1278.3722575</v>
+        <v>1269.445455</v>
       </c>
       <c r="O59">
-        <v>281.24189665</v>
+        <v>279.2780001</v>
       </c>
       <c r="P59">
-        <v>997.13036085</v>
+        <v>990.1674549000001</v>
       </c>
       <c r="Q59">
-        <v>2140.83036085</v>
+        <v>2133.8674549</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1533989927573496</v>
+        <v>0.1556837709512106</v>
       </c>
       <c r="T59">
-        <v>1.481140636101936</v>
+        <v>1.512591467942329</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.512387102202863</v>
+        <v>3.451828703889021</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09040490379950844</v>
+        <v>0.09026186071335654</v>
       </c>
       <c r="C60">
-        <v>8047.619183064531</v>
+        <v>7910.231647693259</v>
       </c>
       <c r="D60">
-        <v>14549.16918306453</v>
+        <v>14573.20664769326</v>
       </c>
       <c r="E60">
-        <v>4013.849999999999</v>
+        <v>4175.274999999999</v>
       </c>
       <c r="F60">
-        <v>9362.65</v>
+        <v>9524.074999999999</v>
       </c>
       <c r="G60">
         <v>2861.1</v>
@@ -6207,28 +6207,28 @@
         <v>1787.2</v>
       </c>
       <c r="M60">
-        <v>517.754545</v>
+        <v>526.6813474999999</v>
       </c>
       <c r="N60">
-        <v>1269.445455</v>
+        <v>1260.5186525</v>
       </c>
       <c r="O60">
-        <v>279.2780001</v>
+        <v>277.31410355</v>
       </c>
       <c r="P60">
-        <v>990.1674549000001</v>
+        <v>983.2045489500001</v>
       </c>
       <c r="Q60">
-        <v>2133.8674549</v>
+        <v>2126.90454895</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1556837709512105</v>
+        <v>0.1580800017398939</v>
       </c>
       <c r="T60">
-        <v>1.512591467942328</v>
+        <v>1.545576486701765</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.451828703889022</v>
+        <v>3.393323132636666</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09026186071335654</v>
+        <v>0.09011881762720461</v>
       </c>
       <c r="C61">
-        <v>7910.231647693259</v>
+        <v>7772.923670940389</v>
       </c>
       <c r="D61">
-        <v>14573.20664769326</v>
+        <v>14597.32367094039</v>
       </c>
       <c r="E61">
-        <v>4175.274999999999</v>
+        <v>4336.7</v>
       </c>
       <c r="F61">
-        <v>9524.074999999999</v>
+        <v>9685.5</v>
       </c>
       <c r="G61">
         <v>2861.1</v>
@@ -6289,28 +6289,28 @@
         <v>1787.2</v>
       </c>
       <c r="M61">
-        <v>526.6813474999999</v>
+        <v>535.60815</v>
       </c>
       <c r="N61">
-        <v>1260.5186525</v>
+        <v>1251.59185</v>
       </c>
       <c r="O61">
-        <v>277.31410355</v>
+        <v>275.350207</v>
       </c>
       <c r="P61">
-        <v>983.2045489500001</v>
+        <v>976.2416430000001</v>
       </c>
       <c r="Q61">
-        <v>2126.90454895</v>
+        <v>2119.941643</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1580800017398939</v>
+        <v>0.1605960440680115</v>
       </c>
       <c r="T61">
-        <v>1.545576486701765</v>
+        <v>1.580210756399173</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.393323132636666</v>
+        <v>3.336767747092721</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09011881762720461</v>
+        <v>0.08997577454105271</v>
       </c>
       <c r="C62">
-        <v>7772.923670940389</v>
+        <v>7635.69564844243</v>
       </c>
       <c r="D62">
-        <v>14597.32367094039</v>
+        <v>14621.52064844243</v>
       </c>
       <c r="E62">
-        <v>4336.7</v>
+        <v>4498.124999999999</v>
       </c>
       <c r="F62">
-        <v>9685.5</v>
+        <v>9846.924999999999</v>
       </c>
       <c r="G62">
         <v>2861.1</v>
@@ -6371,28 +6371,28 @@
         <v>1787.2</v>
       </c>
       <c r="M62">
-        <v>535.60815</v>
+        <v>544.5349525</v>
       </c>
       <c r="N62">
-        <v>1251.59185</v>
+        <v>1242.6650475</v>
       </c>
       <c r="O62">
-        <v>275.350207</v>
+        <v>273.3863104500001</v>
       </c>
       <c r="P62">
-        <v>976.2416430000001</v>
+        <v>969.27873705</v>
       </c>
       <c r="Q62">
-        <v>2119.941643</v>
+        <v>2112.97873705</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1605960440680115</v>
+        <v>0.1632411142078275</v>
       </c>
       <c r="T62">
-        <v>1.580210756399173</v>
+        <v>1.616621142491319</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.336767747092721</v>
+        <v>3.282066636484644</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08997577454105271</v>
+        <v>0.08983273145490081</v>
       </c>
       <c r="C63">
-        <v>7635.69564844243</v>
+        <v>7498.547978463537</v>
       </c>
       <c r="D63">
-        <v>14621.52064844243</v>
+        <v>14645.79797846354</v>
       </c>
       <c r="E63">
-        <v>4498.124999999999</v>
+        <v>4659.55</v>
       </c>
       <c r="F63">
-        <v>9846.924999999999</v>
+        <v>10008.35</v>
       </c>
       <c r="G63">
         <v>2861.1</v>
@@ -6453,28 +6453,28 @@
         <v>1787.2</v>
       </c>
       <c r="M63">
-        <v>544.5349525</v>
+        <v>553.461755</v>
       </c>
       <c r="N63">
-        <v>1242.6650475</v>
+        <v>1233.738245</v>
       </c>
       <c r="O63">
-        <v>273.3863104500001</v>
+        <v>271.4224139</v>
       </c>
       <c r="P63">
-        <v>969.27873705</v>
+        <v>962.3158311</v>
       </c>
       <c r="Q63">
-        <v>2112.97873705</v>
+        <v>2106.0158311</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1632411142078275</v>
+        <v>0.1660253985655284</v>
       </c>
       <c r="T63">
-        <v>1.616621142491319</v>
+        <v>1.654947864693579</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.282066636484644</v>
+        <v>3.229130077831665</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08983273145490081</v>
+        <v>0.08968968836874892</v>
       </c>
       <c r="C64">
-        <v>7498.547978463537</v>
+        <v>7361.481061917339</v>
       </c>
       <c r="D64">
-        <v>14645.79797846354</v>
+        <v>14670.15606191734</v>
       </c>
       <c r="E64">
-        <v>4659.55</v>
+        <v>4820.974999999999</v>
       </c>
       <c r="F64">
-        <v>10008.35</v>
+        <v>10169.775</v>
       </c>
       <c r="G64">
         <v>2861.1</v>
@@ -6535,28 +6535,28 @@
         <v>1787.2</v>
       </c>
       <c r="M64">
-        <v>553.461755</v>
+        <v>562.3885575</v>
       </c>
       <c r="N64">
-        <v>1233.738245</v>
+        <v>1224.8114425</v>
       </c>
       <c r="O64">
-        <v>271.4224139</v>
+        <v>269.45851735</v>
       </c>
       <c r="P64">
-        <v>962.3158311</v>
+        <v>955.3529251499999</v>
       </c>
       <c r="Q64">
-        <v>2106.0158311</v>
+        <v>2099.05292515</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1660253985655284</v>
+        <v>0.1689601847804025</v>
       </c>
       <c r="T64">
-        <v>1.654947864693579</v>
+        <v>1.695346301609475</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.229130077831665</v>
+        <v>3.17787404485021</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08968968836874892</v>
+        <v>0.08954664528259702</v>
       </c>
       <c r="C65">
-        <v>7361.481061917339</v>
+        <v>7224.495302389027</v>
       </c>
       <c r="D65">
-        <v>14670.15606191734</v>
+        <v>14694.59530238903</v>
       </c>
       <c r="E65">
-        <v>4820.974999999999</v>
+        <v>4982.400000000001</v>
       </c>
       <c r="F65">
-        <v>10169.775</v>
+        <v>10331.2</v>
       </c>
       <c r="G65">
         <v>2861.1</v>
@@ -6617,28 +6617,28 @@
         <v>1787.2</v>
       </c>
       <c r="M65">
-        <v>562.3885575</v>
+        <v>571.3153600000001</v>
       </c>
       <c r="N65">
-        <v>1224.8114425</v>
+        <v>1215.88464</v>
       </c>
       <c r="O65">
-        <v>269.45851735</v>
+        <v>267.4946208</v>
       </c>
       <c r="P65">
-        <v>955.3529251499999</v>
+        <v>948.3900192</v>
       </c>
       <c r="Q65">
-        <v>2099.05292515</v>
+        <v>2092.0900192</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1689601847804025</v>
+        <v>0.1720580146738806</v>
       </c>
       <c r="T65">
-        <v>1.695346301609475</v>
+        <v>1.737989096131809</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.17787404485021</v>
+        <v>3.128219762899425</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08954664528259702</v>
+        <v>0.08940360219644512</v>
       </c>
       <c r="C66">
-        <v>7224.495302389027</v>
+        <v>7087.591106157633</v>
       </c>
       <c r="D66">
-        <v>14694.59530238903</v>
+        <v>14719.11610615763</v>
       </c>
       <c r="E66">
-        <v>4982.400000000001</v>
+        <v>5143.825</v>
       </c>
       <c r="F66">
-        <v>10331.2</v>
+        <v>10492.625</v>
       </c>
       <c r="G66">
         <v>2861.1</v>
@@ -6699,28 +6699,28 @@
         <v>1787.2</v>
       </c>
       <c r="M66">
-        <v>571.3153600000001</v>
+        <v>580.2421625000001</v>
       </c>
       <c r="N66">
-        <v>1215.88464</v>
+        <v>1206.9578375</v>
       </c>
       <c r="O66">
-        <v>267.4946208</v>
+        <v>265.53072425</v>
       </c>
       <c r="P66">
-        <v>948.3900192</v>
+        <v>941.42711325</v>
       </c>
       <c r="Q66">
-        <v>2092.0900192</v>
+        <v>2085.12711325</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1720580146738806</v>
+        <v>0.1753328634184146</v>
       </c>
       <c r="T66">
-        <v>1.737989096131809</v>
+        <v>1.783068621769705</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.128219762899425</v>
+        <v>3.080093305008665</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08940360219644512</v>
+        <v>0.08926055911029324</v>
       </c>
       <c r="C67">
-        <v>7087.591106157633</v>
+        <v>6950.768882218543</v>
       </c>
       <c r="D67">
-        <v>14719.11610615763</v>
+        <v>14743.71888221854</v>
       </c>
       <c r="E67">
-        <v>5143.825</v>
+        <v>5305.250000000001</v>
       </c>
       <c r="F67">
-        <v>10492.625</v>
+        <v>10654.05</v>
       </c>
       <c r="G67">
         <v>2861.1</v>
@@ -6781,28 +6781,28 @@
         <v>1787.2</v>
       </c>
       <c r="M67">
-        <v>580.2421625000001</v>
+        <v>589.1689650000001</v>
       </c>
       <c r="N67">
-        <v>1206.9578375</v>
+        <v>1198.031035</v>
       </c>
       <c r="O67">
-        <v>265.53072425</v>
+        <v>263.5668277</v>
       </c>
       <c r="P67">
-        <v>941.42711325</v>
+        <v>934.4642073</v>
       </c>
       <c r="Q67">
-        <v>2085.12711325</v>
+        <v>2078.1642073</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1753328634184146</v>
+        <v>0.1788003503243918</v>
       </c>
       <c r="T67">
-        <v>1.783068621769705</v>
+        <v>1.830799884209831</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.080093305008665</v>
+        <v>3.033425224629746</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08926055911029324</v>
+        <v>0.09042401602414132</v>
       </c>
       <c r="C68">
-        <v>6950.768882218543</v>
+        <v>6591.588501363001</v>
       </c>
       <c r="D68">
-        <v>14743.71888221854</v>
+        <v>14545.963501363</v>
       </c>
       <c r="E68">
-        <v>5305.250000000001</v>
+        <v>5466.675</v>
       </c>
       <c r="F68">
-        <v>10654.05</v>
+        <v>10815.475</v>
       </c>
       <c r="G68">
         <v>2861.1</v>
@@ -6863,45 +6863,45 @@
         <v>1787.2</v>
       </c>
       <c r="M68">
-        <v>589.1689650000001</v>
+        <v>625.1344550000001</v>
       </c>
       <c r="N68">
-        <v>1198.031035</v>
+        <v>1162.065545</v>
       </c>
       <c r="O68">
-        <v>263.5668277</v>
+        <v>255.6544199</v>
       </c>
       <c r="P68">
-        <v>934.4642073</v>
+        <v>906.4111250999999</v>
       </c>
       <c r="Q68">
-        <v>2078.1642073</v>
+        <v>2050.1111251</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1788003503243918</v>
+        <v>0.1824779879519434</v>
       </c>
       <c r="T68">
-        <v>1.830799884209831</v>
+        <v>1.881423950434206</v>
       </c>
       <c r="U68">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.22</v>
       </c>
       <c r="W68">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.033425224629746</v>
+        <v>2.858904969491723</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09042401602414132</v>
+        <v>0.09030047293798943</v>
       </c>
       <c r="C69">
-        <v>6591.588501363001</v>
+        <v>6450.910290444965</v>
       </c>
       <c r="D69">
-        <v>14545.963501363</v>
+        <v>14566.71029044497</v>
       </c>
       <c r="E69">
-        <v>5466.675</v>
+        <v>5628.100000000001</v>
       </c>
       <c r="F69">
-        <v>10815.475</v>
+        <v>10976.9</v>
       </c>
       <c r="G69">
         <v>2861.1</v>
@@ -6945,28 +6945,28 @@
         <v>1787.2</v>
       </c>
       <c r="M69">
-        <v>625.1344550000001</v>
+        <v>634.4648200000001</v>
       </c>
       <c r="N69">
-        <v>1162.065545</v>
+        <v>1152.73518</v>
       </c>
       <c r="O69">
-        <v>255.6544199</v>
+        <v>253.6017396</v>
       </c>
       <c r="P69">
-        <v>906.4111250999999</v>
+        <v>899.1334403999999</v>
       </c>
       <c r="Q69">
-        <v>2050.1111251</v>
+        <v>2042.8334404</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1824779879519434</v>
+        <v>0.186385477931217</v>
       </c>
       <c r="T69">
-        <v>1.881423950434206</v>
+        <v>1.935212020797605</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.858904969491723</v>
+        <v>2.816862249352138</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09030047293798943</v>
+        <v>0.09017692985183752</v>
       </c>
       <c r="C70">
-        <v>6450.910290444965</v>
+        <v>6310.291346010283</v>
       </c>
       <c r="D70">
-        <v>14566.71029044497</v>
+        <v>14587.51634601028</v>
       </c>
       <c r="E70">
-        <v>5628.100000000001</v>
+        <v>5789.525000000001</v>
       </c>
       <c r="F70">
-        <v>10976.9</v>
+        <v>11138.325</v>
       </c>
       <c r="G70">
         <v>2861.1</v>
@@ -7027,28 +7027,28 @@
         <v>1787.2</v>
       </c>
       <c r="M70">
-        <v>634.4648200000001</v>
+        <v>643.7951850000001</v>
       </c>
       <c r="N70">
-        <v>1152.73518</v>
+        <v>1143.404815</v>
       </c>
       <c r="O70">
-        <v>253.6017396</v>
+        <v>251.5490593</v>
       </c>
       <c r="P70">
-        <v>899.1334403999999</v>
+        <v>891.8557556999999</v>
       </c>
       <c r="Q70">
-        <v>2042.8334404</v>
+        <v>2035.5557557</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.186385477931217</v>
+        <v>0.1905450640381856</v>
       </c>
       <c r="T70">
-        <v>1.935212020797605</v>
+        <v>1.992470289248965</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.816862249352138</v>
+        <v>2.776038158781818</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09017692985183752</v>
+        <v>0.09005338676568561</v>
       </c>
       <c r="C71">
-        <v>6310.291346010283</v>
+        <v>6169.731922378325</v>
       </c>
       <c r="D71">
-        <v>14587.51634601028</v>
+        <v>14608.38192237833</v>
       </c>
       <c r="E71">
-        <v>5789.525000000001</v>
+        <v>5950.950000000002</v>
       </c>
       <c r="F71">
-        <v>11138.325</v>
+        <v>11299.75</v>
       </c>
       <c r="G71">
         <v>2861.1</v>
@@ -7109,28 +7109,28 @@
         <v>1787.2</v>
       </c>
       <c r="M71">
-        <v>643.7951850000001</v>
+        <v>653.1255500000002</v>
       </c>
       <c r="N71">
-        <v>1143.404815</v>
+        <v>1134.07445</v>
       </c>
       <c r="O71">
-        <v>251.5490593</v>
+        <v>249.496379</v>
       </c>
       <c r="P71">
-        <v>891.8557556999999</v>
+        <v>884.5780709999999</v>
       </c>
       <c r="Q71">
-        <v>2035.5557557</v>
+        <v>2028.278071</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1905450640381856</v>
+        <v>0.1949819558856187</v>
       </c>
       <c r="T71">
-        <v>1.992470289248965</v>
+        <v>2.053545775597082</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.776038158781818</v>
+        <v>2.73638047079922</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09005338676568561</v>
+        <v>0.08992984367953372</v>
       </c>
       <c r="C72">
-        <v>6169.731922378325</v>
+        <v>6029.232275325625</v>
       </c>
       <c r="D72">
-        <v>14608.38192237833</v>
+        <v>14629.30727532563</v>
       </c>
       <c r="E72">
-        <v>5950.950000000002</v>
+        <v>6112.375000000001</v>
       </c>
       <c r="F72">
-        <v>11299.75</v>
+        <v>11461.175</v>
       </c>
       <c r="G72">
         <v>2861.1</v>
@@ -7191,28 +7191,28 @@
         <v>1787.2</v>
       </c>
       <c r="M72">
-        <v>653.1255500000002</v>
+        <v>662.4559150000001</v>
       </c>
       <c r="N72">
-        <v>1134.07445</v>
+        <v>1124.744085</v>
       </c>
       <c r="O72">
-        <v>249.496379</v>
+        <v>247.4436987</v>
       </c>
       <c r="P72">
-        <v>884.5780709999999</v>
+        <v>877.3003862999999</v>
       </c>
       <c r="Q72">
-        <v>2028.278071</v>
+        <v>2021.0003863</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1949819558856187</v>
+        <v>0.1997248402742542</v>
       </c>
       <c r="T72">
-        <v>2.053545775597082</v>
+        <v>2.118833364451966</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.73638047079922</v>
+        <v>2.697839900787963</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08992984367953372</v>
+        <v>0.08980630059338182</v>
       </c>
       <c r="C73">
-        <v>6029.232275325627</v>
+        <v>5888.792662096357</v>
       </c>
       <c r="D73">
-        <v>14629.30727532563</v>
+        <v>14650.29266209636</v>
       </c>
       <c r="E73">
-        <v>6112.374999999999</v>
+        <v>6273.8</v>
       </c>
       <c r="F73">
-        <v>11461.175</v>
+        <v>11622.6</v>
       </c>
       <c r="G73">
         <v>2861.1</v>
@@ -7273,28 +7273,28 @@
         <v>1787.2</v>
       </c>
       <c r="M73">
-        <v>662.455915</v>
+        <v>671.78628</v>
       </c>
       <c r="N73">
-        <v>1124.744085</v>
+        <v>1115.41372</v>
       </c>
       <c r="O73">
-        <v>247.4436987</v>
+        <v>245.3910184</v>
       </c>
       <c r="P73">
-        <v>877.3003863</v>
+        <v>870.0227016</v>
       </c>
       <c r="Q73">
-        <v>2021.0003863</v>
+        <v>2013.7227016</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1997248402742542</v>
+        <v>0.2048065021192208</v>
       </c>
       <c r="T73">
-        <v>2.118833364451965</v>
+        <v>2.18878435251077</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.697839900787964</v>
+        <v>2.660369902165909</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08980630059338182</v>
+        <v>0.0896827575072299</v>
       </c>
       <c r="C74">
-        <v>5888.792662096357</v>
+        <v>5748.413341412843</v>
       </c>
       <c r="D74">
-        <v>14650.29266209636</v>
+        <v>14671.33834141284</v>
       </c>
       <c r="E74">
-        <v>6273.8</v>
+        <v>6435.224999999999</v>
       </c>
       <c r="F74">
-        <v>11622.6</v>
+        <v>11784.025</v>
       </c>
       <c r="G74">
         <v>2861.1</v>
@@ -7355,28 +7355,28 @@
         <v>1787.2</v>
       </c>
       <c r="M74">
-        <v>671.78628</v>
+        <v>681.1166450000001</v>
       </c>
       <c r="N74">
-        <v>1115.41372</v>
+        <v>1106.083355</v>
       </c>
       <c r="O74">
-        <v>245.3910184</v>
+        <v>243.3383381</v>
       </c>
       <c r="P74">
-        <v>870.0227016</v>
+        <v>862.7450169</v>
       </c>
       <c r="Q74">
-        <v>2013.7227016</v>
+        <v>2006.4450169</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2048065021192208</v>
+        <v>0.2102645833601108</v>
       </c>
       <c r="T74">
-        <v>2.18878435251077</v>
+        <v>2.263916895240596</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.660369902165909</v>
+        <v>2.623926478848568</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0896827575072299</v>
+        <v>0.089559214421078</v>
       </c>
       <c r="C75">
-        <v>5748.413341412843</v>
+        <v>5608.094573486196</v>
       </c>
       <c r="D75">
-        <v>14671.33834141284</v>
+        <v>14692.4445734862</v>
       </c>
       <c r="E75">
-        <v>6435.224999999999</v>
+        <v>6596.650000000001</v>
       </c>
       <c r="F75">
-        <v>11784.025</v>
+        <v>11945.45</v>
       </c>
       <c r="G75">
         <v>2861.1</v>
@@ -7437,28 +7437,28 @@
         <v>1787.2</v>
       </c>
       <c r="M75">
-        <v>681.1166450000001</v>
+        <v>690.4470100000001</v>
       </c>
       <c r="N75">
-        <v>1106.083355</v>
+        <v>1096.75299</v>
       </c>
       <c r="O75">
-        <v>243.3383381</v>
+        <v>241.2856578</v>
       </c>
       <c r="P75">
-        <v>862.7450169</v>
+        <v>855.4673322</v>
       </c>
       <c r="Q75">
-        <v>2006.4450169</v>
+        <v>1999.1673322</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2102645833601108</v>
+        <v>0.2161425170041462</v>
       </c>
       <c r="T75">
-        <v>2.263916895240596</v>
+        <v>2.344828864334256</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.623926478848568</v>
+        <v>2.588468012918182</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.089559214421078</v>
+        <v>0.08943567133492611</v>
       </c>
       <c r="C76">
-        <v>5608.094573486196</v>
+        <v>5467.836620027061</v>
       </c>
       <c r="D76">
-        <v>14692.4445734862</v>
+        <v>14713.61162002706</v>
       </c>
       <c r="E76">
-        <v>6596.650000000001</v>
+        <v>6758.075</v>
       </c>
       <c r="F76">
-        <v>11945.45</v>
+        <v>12106.875</v>
       </c>
       <c r="G76">
         <v>2861.1</v>
@@ -7519,28 +7519,28 @@
         <v>1787.2</v>
       </c>
       <c r="M76">
-        <v>690.4470100000001</v>
+        <v>699.777375</v>
       </c>
       <c r="N76">
-        <v>1096.75299</v>
+        <v>1087.422625</v>
       </c>
       <c r="O76">
-        <v>241.2856578</v>
+        <v>239.2329775</v>
       </c>
       <c r="P76">
-        <v>855.4673322</v>
+        <v>848.1896475000001</v>
       </c>
       <c r="Q76">
-        <v>1999.1673322</v>
+        <v>1991.8896475</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2161425170041462</v>
+        <v>0.2224906853397044</v>
       </c>
       <c r="T76">
-        <v>2.344828864334256</v>
+        <v>2.432213790955408</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.588468012918182</v>
+        <v>2.553955106079273</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08943567133492611</v>
+        <v>0.08931212824877421</v>
       </c>
       <c r="C77">
-        <v>5467.836620027061</v>
+        <v>5327.639744256416</v>
       </c>
       <c r="D77">
-        <v>14713.61162002706</v>
+        <v>14734.83974425642</v>
       </c>
       <c r="E77">
-        <v>6758.075</v>
+        <v>6919.499999999999</v>
       </c>
       <c r="F77">
-        <v>12106.875</v>
+        <v>12268.3</v>
       </c>
       <c r="G77">
         <v>2861.1</v>
@@ -7601,28 +7601,28 @@
         <v>1787.2</v>
       </c>
       <c r="M77">
-        <v>699.777375</v>
+        <v>709.10774</v>
       </c>
       <c r="N77">
-        <v>1087.422625</v>
+        <v>1078.09226</v>
       </c>
       <c r="O77">
-        <v>239.2329775</v>
+        <v>237.1802972</v>
       </c>
       <c r="P77">
-        <v>848.1896475000001</v>
+        <v>840.9119627999999</v>
       </c>
       <c r="Q77">
-        <v>1991.8896475</v>
+        <v>1984.6119628</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2224906853397044</v>
+        <v>0.2293678677032259</v>
       </c>
       <c r="T77">
-        <v>2.432213790955408</v>
+        <v>2.526880794794991</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.553955106079273</v>
+        <v>2.520350433630861</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08931212824877421</v>
+        <v>0.0912906851626223</v>
       </c>
       <c r="C78">
-        <v>5327.639744256416</v>
+        <v>4833.442365118715</v>
       </c>
       <c r="D78">
-        <v>14734.83974425642</v>
+        <v>14402.06736511872</v>
       </c>
       <c r="E78">
-        <v>6919.499999999999</v>
+        <v>7080.925</v>
       </c>
       <c r="F78">
-        <v>12268.3</v>
+        <v>12429.725</v>
       </c>
       <c r="G78">
         <v>2861.1</v>
@@ -7683,45 +7683,45 @@
         <v>1787.2</v>
       </c>
       <c r="M78">
-        <v>709.10774</v>
+        <v>761.9421425</v>
       </c>
       <c r="N78">
-        <v>1078.09226</v>
+        <v>1025.2578575</v>
       </c>
       <c r="O78">
-        <v>237.1802972</v>
+        <v>225.55672865</v>
       </c>
       <c r="P78">
-        <v>840.9119627999999</v>
+        <v>799.70112885</v>
       </c>
       <c r="Q78">
-        <v>1984.6119628</v>
+        <v>1943.40112885</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2293678677032259</v>
+        <v>0.2368430659244448</v>
       </c>
       <c r="T78">
-        <v>2.526880794794991</v>
+        <v>2.629779712011927</v>
       </c>
       <c r="U78">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V78">
         <v>0.22</v>
       </c>
       <c r="W78">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.520350433630861</v>
+        <v>2.345584920839314</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0912906851626223</v>
+        <v>0.0911944420764704</v>
       </c>
       <c r="C79">
-        <v>4833.442365118715</v>
+        <v>4687.856266178986</v>
       </c>
       <c r="D79">
-        <v>14402.06736511872</v>
+        <v>14417.90626617898</v>
       </c>
       <c r="E79">
-        <v>7080.925</v>
+        <v>7242.349999999999</v>
       </c>
       <c r="F79">
-        <v>12429.725</v>
+        <v>12591.15</v>
       </c>
       <c r="G79">
         <v>2861.1</v>
@@ -7765,28 +7765,28 @@
         <v>1787.2</v>
       </c>
       <c r="M79">
-        <v>761.9421425</v>
+        <v>771.837495</v>
       </c>
       <c r="N79">
-        <v>1025.2578575</v>
+        <v>1015.362505</v>
       </c>
       <c r="O79">
-        <v>225.55672865</v>
+        <v>223.3797511</v>
       </c>
       <c r="P79">
-        <v>799.70112885</v>
+        <v>791.9827539</v>
       </c>
       <c r="Q79">
-        <v>1943.40112885</v>
+        <v>1935.6827539</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2368430659244448</v>
+        <v>0.24499782762032</v>
       </c>
       <c r="T79">
-        <v>2.629779712011927</v>
+        <v>2.742033076248586</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.345584920839314</v>
+        <v>2.315513319290092</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0911944420764704</v>
+        <v>0.09109819899031851</v>
       </c>
       <c r="C80">
-        <v>4687.856266178986</v>
+        <v>4542.305043758479</v>
       </c>
       <c r="D80">
-        <v>14417.90626617898</v>
+        <v>14433.78004375848</v>
       </c>
       <c r="E80">
-        <v>7242.349999999999</v>
+        <v>7403.775000000001</v>
       </c>
       <c r="F80">
-        <v>12591.15</v>
+        <v>12752.575</v>
       </c>
       <c r="G80">
         <v>2861.1</v>
@@ -7847,28 +7847,28 @@
         <v>1787.2</v>
       </c>
       <c r="M80">
-        <v>771.837495</v>
+        <v>781.7328475</v>
       </c>
       <c r="N80">
-        <v>1015.362505</v>
+        <v>1005.4671525</v>
       </c>
       <c r="O80">
-        <v>223.3797511</v>
+        <v>221.20277355</v>
       </c>
       <c r="P80">
-        <v>791.9827539</v>
+        <v>784.26437895</v>
       </c>
       <c r="Q80">
-        <v>1935.6827539</v>
+        <v>1927.96437895</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.24499782762032</v>
+        <v>0.253929233287231</v>
       </c>
       <c r="T80">
-        <v>2.742033076248586</v>
+        <v>2.864977237079211</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.315513319290092</v>
+        <v>2.286203024109205</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09109819899031851</v>
+        <v>0.0910019559041666</v>
       </c>
       <c r="C81">
-        <v>4542.305043758479</v>
+        <v>4396.788813178868</v>
       </c>
       <c r="D81">
-        <v>14433.78004375848</v>
+        <v>14449.68881317887</v>
       </c>
       <c r="E81">
-        <v>7403.775000000001</v>
+        <v>7565.2</v>
       </c>
       <c r="F81">
-        <v>12752.575</v>
+        <v>12914</v>
       </c>
       <c r="G81">
         <v>2861.1</v>
@@ -7929,28 +7929,28 @@
         <v>1787.2</v>
       </c>
       <c r="M81">
-        <v>781.7328475</v>
+        <v>791.6282</v>
       </c>
       <c r="N81">
-        <v>1005.4671525</v>
+        <v>995.5718000000001</v>
       </c>
       <c r="O81">
-        <v>221.20277355</v>
+        <v>219.025796</v>
       </c>
       <c r="P81">
-        <v>784.26437895</v>
+        <v>776.546004</v>
       </c>
       <c r="Q81">
-        <v>1927.96437895</v>
+        <v>1920.246004</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.253929233287231</v>
+        <v>0.2637537795208331</v>
       </c>
       <c r="T81">
-        <v>2.864977237079211</v>
+        <v>3.0002158139929</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.286203024109205</v>
+        <v>2.25762548630784</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0910019559041666</v>
+        <v>0.09267475281801471</v>
       </c>
       <c r="C82">
-        <v>4396.788813178868</v>
+        <v>3963.752700655861</v>
       </c>
       <c r="D82">
-        <v>14449.68881317887</v>
+        <v>14178.07770065586</v>
       </c>
       <c r="E82">
-        <v>7565.2</v>
+        <v>7726.625000000001</v>
       </c>
       <c r="F82">
-        <v>12914</v>
+        <v>13075.425</v>
       </c>
       <c r="G82">
         <v>2861.1</v>
@@ -8011,45 +8011,45 @@
         <v>1787.2</v>
       </c>
       <c r="M82">
-        <v>791.6282</v>
+        <v>838.1347425000001</v>
       </c>
       <c r="N82">
-        <v>995.5718000000001</v>
+        <v>949.0652574999999</v>
       </c>
       <c r="O82">
-        <v>219.025796</v>
+        <v>208.79435665</v>
       </c>
       <c r="P82">
-        <v>776.546004</v>
+        <v>740.27090085</v>
       </c>
       <c r="Q82">
-        <v>1920.246004</v>
+        <v>1883.97090085</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2637537795208331</v>
+        <v>0.2746124885158669</v>
       </c>
       <c r="T82">
-        <v>3.0002158139929</v>
+        <v>3.149690030581713</v>
       </c>
       <c r="U82">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V82">
         <v>0.22</v>
       </c>
       <c r="W82">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.25762548630784</v>
+        <v>2.132354034948026</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09267475281801471</v>
+        <v>0.09260034973186279</v>
       </c>
       <c r="C83">
-        <v>3963.752700655861</v>
+        <v>3814.191324580412</v>
       </c>
       <c r="D83">
-        <v>14178.07770065586</v>
+        <v>14189.94132458041</v>
       </c>
       <c r="E83">
-        <v>7726.625000000001</v>
+        <v>7888.05</v>
       </c>
       <c r="F83">
-        <v>13075.425</v>
+        <v>13236.85</v>
       </c>
       <c r="G83">
         <v>2861.1</v>
@@ -8093,28 +8093,28 @@
         <v>1787.2</v>
       </c>
       <c r="M83">
-        <v>838.1347425000001</v>
+        <v>848.4820850000001</v>
       </c>
       <c r="N83">
-        <v>949.0652574999999</v>
+        <v>938.7179149999999</v>
       </c>
       <c r="O83">
-        <v>208.79435665</v>
+        <v>206.5179413</v>
       </c>
       <c r="P83">
-        <v>740.27090085</v>
+        <v>732.1999737</v>
       </c>
       <c r="Q83">
-        <v>1883.97090085</v>
+        <v>1875.8999737</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2746124885158669</v>
+        <v>0.2866777207325711</v>
       </c>
       <c r="T83">
-        <v>3.149690030581713</v>
+        <v>3.315772493458172</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.132354034948026</v>
+        <v>2.10634971744866</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09260034973186279</v>
+        <v>0.0925259466457109</v>
       </c>
       <c r="C84">
-        <v>3814.191324580412</v>
+        <v>3664.649819102968</v>
       </c>
       <c r="D84">
-        <v>14189.94132458041</v>
+        <v>14201.82481910297</v>
       </c>
       <c r="E84">
-        <v>7888.05</v>
+        <v>8049.475000000001</v>
       </c>
       <c r="F84">
-        <v>13236.85</v>
+        <v>13398.275</v>
       </c>
       <c r="G84">
         <v>2861.1</v>
@@ -8175,28 +8175,28 @@
         <v>1787.2</v>
       </c>
       <c r="M84">
-        <v>848.4820850000001</v>
+        <v>858.8294275000002</v>
       </c>
       <c r="N84">
-        <v>938.7179149999999</v>
+        <v>928.3705724999999</v>
       </c>
       <c r="O84">
-        <v>206.5179413</v>
+        <v>204.24152595</v>
       </c>
       <c r="P84">
-        <v>732.1999737</v>
+        <v>724.1290465499999</v>
       </c>
       <c r="Q84">
-        <v>1875.8999737</v>
+        <v>1867.82904655</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2866777207325711</v>
+        <v>0.3001623920335936</v>
       </c>
       <c r="T84">
-        <v>3.315772493458172</v>
+        <v>3.501394069614216</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.10634971744866</v>
+        <v>2.080972010009519</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0925259466457109</v>
+        <v>0.09245154355955901</v>
       </c>
       <c r="C85">
-        <v>3664.649819102968</v>
+        <v>3515.12823418781</v>
       </c>
       <c r="D85">
-        <v>14201.82481910297</v>
+        <v>14213.72823418781</v>
       </c>
       <c r="E85">
-        <v>8049.475000000001</v>
+        <v>8210.900000000001</v>
       </c>
       <c r="F85">
-        <v>13398.275</v>
+        <v>13559.7</v>
       </c>
       <c r="G85">
         <v>2861.1</v>
@@ -8257,28 +8257,28 @@
         <v>1787.2</v>
       </c>
       <c r="M85">
-        <v>858.8294275000002</v>
+        <v>869.1767700000001</v>
       </c>
       <c r="N85">
-        <v>928.3705724999999</v>
+        <v>918.0232299999999</v>
       </c>
       <c r="O85">
-        <v>204.24152595</v>
+        <v>201.9651106</v>
       </c>
       <c r="P85">
-        <v>724.1290465499999</v>
+        <v>716.0581193999999</v>
       </c>
       <c r="Q85">
-        <v>1867.82904655</v>
+        <v>1859.7581194</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3001623920335936</v>
+        <v>0.3153326472472439</v>
       </c>
       <c r="T85">
-        <v>3.501394069614216</v>
+        <v>3.710218342789765</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.080972010009519</v>
+        <v>2.056198533699882</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09245154355955901</v>
+        <v>0.0923771404734071</v>
       </c>
       <c r="C86">
-        <v>3515.128234187812</v>
+        <v>3365.626619966875</v>
       </c>
       <c r="D86">
-        <v>14213.72823418781</v>
+        <v>14225.65161996688</v>
       </c>
       <c r="E86">
-        <v>8210.899999999998</v>
+        <v>8372.325000000001</v>
       </c>
       <c r="F86">
-        <v>13559.7</v>
+        <v>13721.125</v>
       </c>
       <c r="G86">
         <v>2861.1</v>
@@ -8339,28 +8339,28 @@
         <v>1787.2</v>
       </c>
       <c r="M86">
-        <v>869.17677</v>
+        <v>879.5241125</v>
       </c>
       <c r="N86">
-        <v>918.02323</v>
+        <v>907.6758875</v>
       </c>
       <c r="O86">
-        <v>201.9651106</v>
+        <v>199.68869525</v>
       </c>
       <c r="P86">
-        <v>716.0581194</v>
+        <v>707.98719225</v>
       </c>
       <c r="Q86">
-        <v>1859.7581194</v>
+        <v>1851.68719225</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3153326472472437</v>
+        <v>0.3325256031560473</v>
       </c>
       <c r="T86">
-        <v>3.710218342789762</v>
+        <v>3.946885852388717</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.056198533699883</v>
+        <v>2.032007962715178</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0923771404734071</v>
+        <v>0.0923027373872552</v>
       </c>
       <c r="C87">
-        <v>3365.626619966875</v>
+        <v>3216.145026740454</v>
       </c>
       <c r="D87">
-        <v>14225.65161996688</v>
+        <v>14237.59502674045</v>
       </c>
       <c r="E87">
-        <v>8372.325000000001</v>
+        <v>8533.75</v>
       </c>
       <c r="F87">
-        <v>13721.125</v>
+        <v>13882.55</v>
       </c>
       <c r="G87">
         <v>2861.1</v>
@@ -8421,28 +8421,28 @@
         <v>1787.2</v>
       </c>
       <c r="M87">
-        <v>879.5241125</v>
+        <v>889.871455</v>
       </c>
       <c r="N87">
-        <v>907.6758875</v>
+        <v>897.3285450000001</v>
       </c>
       <c r="O87">
-        <v>199.68869525</v>
+        <v>197.4122799</v>
       </c>
       <c r="P87">
-        <v>707.98719225</v>
+        <v>699.9162651</v>
       </c>
       <c r="Q87">
-        <v>1851.68719225</v>
+        <v>1843.6162651</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3325256031560473</v>
+        <v>0.3521746956232514</v>
       </c>
       <c r="T87">
-        <v>3.946885852388717</v>
+        <v>4.217363006216093</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.032007962715178</v>
+        <v>2.008379963148722</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.0923027373872552</v>
+        <v>0.09752141430110328</v>
       </c>
       <c r="C88">
-        <v>3216.145026740454</v>
+        <v>2262.926044605108</v>
       </c>
       <c r="D88">
-        <v>14237.59502674045</v>
+        <v>13445.80104460511</v>
       </c>
       <c r="E88">
-        <v>8533.75</v>
+        <v>8695.174999999999</v>
       </c>
       <c r="F88">
-        <v>13882.55</v>
+        <v>14043.975</v>
       </c>
       <c r="G88">
         <v>2861.1</v>
@@ -8503,45 +8503,45 @@
         <v>1787.2</v>
       </c>
       <c r="M88">
-        <v>889.871455</v>
+        <v>1009.7618025</v>
       </c>
       <c r="N88">
-        <v>897.3285450000001</v>
+        <v>777.4381974999999</v>
       </c>
       <c r="O88">
-        <v>197.4122799</v>
+        <v>171.03640345</v>
       </c>
       <c r="P88">
-        <v>699.9162651</v>
+        <v>606.4017940499999</v>
       </c>
       <c r="Q88">
-        <v>1843.6162651</v>
+        <v>1750.10179405</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3521746956232514</v>
+        <v>0.3748467253931022</v>
       </c>
       <c r="T88">
-        <v>4.217363006216093</v>
+        <v>4.529452029863066</v>
       </c>
       <c r="U88">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V88">
         <v>0.22</v>
       </c>
       <c r="W88">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.008379963148722</v>
+        <v>1.76992236740902</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09752141430110328</v>
+        <v>0.1001848112149514</v>
       </c>
       <c r="C89">
-        <v>2262.926044605108</v>
+        <v>1730.407811855437</v>
       </c>
       <c r="D89">
-        <v>13445.80104460511</v>
+        <v>13074.70781185544</v>
       </c>
       <c r="E89">
-        <v>8695.174999999999</v>
+        <v>8856.599999999999</v>
       </c>
       <c r="F89">
-        <v>14043.975</v>
+        <v>14205.4</v>
       </c>
       <c r="G89">
         <v>2861.1</v>
@@ -8585,45 +8585,45 @@
         <v>1787.2</v>
       </c>
       <c r="M89">
-        <v>1009.7618025</v>
+        <v>1076.76932</v>
       </c>
       <c r="N89">
-        <v>777.4381974999999</v>
+        <v>710.4306799999999</v>
       </c>
       <c r="O89">
-        <v>171.03640345</v>
+        <v>156.2947496</v>
       </c>
       <c r="P89">
-        <v>606.4017940499999</v>
+        <v>554.1359304</v>
       </c>
       <c r="Q89">
-        <v>1750.10179405</v>
+        <v>1697.8359304</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3748467253931022</v>
+        <v>0.4012974267912616</v>
       </c>
       <c r="T89">
-        <v>4.529452029863066</v>
+        <v>4.893555890784535</v>
       </c>
       <c r="U89">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V89">
         <v>0.22</v>
       </c>
       <c r="W89">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.76992236740902</v>
+        <v>1.659779831022674</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1001848112149514</v>
+        <v>0.1002016681287995</v>
       </c>
       <c r="C90">
-        <v>1730.407811855437</v>
+        <v>1566.699345242867</v>
       </c>
       <c r="D90">
-        <v>13074.70781185544</v>
+        <v>13072.42434524287</v>
       </c>
       <c r="E90">
-        <v>8856.599999999999</v>
+        <v>9018.025000000001</v>
       </c>
       <c r="F90">
-        <v>14205.4</v>
+        <v>14366.825</v>
       </c>
       <c r="G90">
         <v>2861.1</v>
@@ -8667,28 +8667,28 @@
         <v>1787.2</v>
       </c>
       <c r="M90">
-        <v>1076.76932</v>
+        <v>1089.005335</v>
       </c>
       <c r="N90">
-        <v>710.4306799999999</v>
+        <v>698.194665</v>
       </c>
       <c r="O90">
-        <v>156.2947496</v>
+        <v>153.6028263</v>
       </c>
       <c r="P90">
-        <v>554.1359304</v>
+        <v>544.5918386999999</v>
       </c>
       <c r="Q90">
-        <v>1697.8359304</v>
+        <v>1688.2918387</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4012974267912616</v>
+        <v>0.4325573466254499</v>
       </c>
       <c r="T90">
-        <v>4.893555890784535</v>
+        <v>5.323860453691725</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.659779831022674</v>
+        <v>1.64113061943815</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1002016681287995</v>
+        <v>0.1002185250426476</v>
       </c>
       <c r="C91">
-        <v>1566.699345242867</v>
+        <v>1402.991676095044</v>
       </c>
       <c r="D91">
-        <v>13072.42434524287</v>
+        <v>13070.14167609504</v>
       </c>
       <c r="E91">
-        <v>9018.025000000001</v>
+        <v>9179.450000000001</v>
       </c>
       <c r="F91">
-        <v>14366.825</v>
+        <v>14528.25</v>
       </c>
       <c r="G91">
         <v>2861.1</v>
@@ -8749,28 +8749,28 @@
         <v>1787.2</v>
       </c>
       <c r="M91">
-        <v>1089.005335</v>
+        <v>1101.24135</v>
       </c>
       <c r="N91">
-        <v>698.194665</v>
+        <v>685.95865</v>
       </c>
       <c r="O91">
-        <v>153.6028263</v>
+        <v>150.910903</v>
       </c>
       <c r="P91">
-        <v>544.5918386999999</v>
+        <v>535.0477470000001</v>
       </c>
       <c r="Q91">
-        <v>1688.2918387</v>
+        <v>1678.747747</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4325573466254499</v>
+        <v>0.470069250426476</v>
       </c>
       <c r="T91">
-        <v>5.323860453691725</v>
+        <v>5.840225929180353</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.64113061943815</v>
+        <v>1.622895834777726</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1002185250426476</v>
+        <v>0.1002353819564957</v>
       </c>
       <c r="C92">
-        <v>1402.991676095044</v>
+        <v>1239.284803994284</v>
       </c>
       <c r="D92">
-        <v>13070.14167609504</v>
+        <v>13067.85980399428</v>
       </c>
       <c r="E92">
-        <v>9179.450000000001</v>
+        <v>9340.875</v>
       </c>
       <c r="F92">
-        <v>14528.25</v>
+        <v>14689.675</v>
       </c>
       <c r="G92">
         <v>2861.1</v>
@@ -8831,28 +8831,28 @@
         <v>1787.2</v>
       </c>
       <c r="M92">
-        <v>1101.24135</v>
+        <v>1113.477365</v>
       </c>
       <c r="N92">
-        <v>685.95865</v>
+        <v>673.7226349999999</v>
       </c>
       <c r="O92">
-        <v>150.910903</v>
+        <v>148.2189797</v>
       </c>
       <c r="P92">
-        <v>535.0477470000001</v>
+        <v>525.5036552999999</v>
       </c>
       <c r="Q92">
-        <v>1678.747747</v>
+        <v>1669.2036553</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.470069250426476</v>
+        <v>0.5159171328499522</v>
       </c>
       <c r="T92">
-        <v>5.840225929180353</v>
+        <v>6.4713392881109</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.622895834777726</v>
+        <v>1.605061814615333</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1002353819564957</v>
+        <v>0.1002522388703438</v>
       </c>
       <c r="C93">
-        <v>1239.284803994284</v>
+        <v>1075.578728523207</v>
       </c>
       <c r="D93">
-        <v>13067.85980399428</v>
+        <v>13065.57872852321</v>
       </c>
       <c r="E93">
-        <v>9340.875</v>
+        <v>9502.299999999999</v>
       </c>
       <c r="F93">
-        <v>14689.675</v>
+        <v>14851.1</v>
       </c>
       <c r="G93">
         <v>2861.1</v>
@@ -8913,28 +8913,28 @@
         <v>1787.2</v>
       </c>
       <c r="M93">
-        <v>1113.477365</v>
+        <v>1125.71338</v>
       </c>
       <c r="N93">
-        <v>673.7226349999999</v>
+        <v>661.4866199999999</v>
       </c>
       <c r="O93">
-        <v>148.2189797</v>
+        <v>145.5270564</v>
       </c>
       <c r="P93">
-        <v>525.5036552999999</v>
+        <v>515.9595635999999</v>
       </c>
       <c r="Q93">
-        <v>1669.2036553</v>
+        <v>1659.6595636</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5159171328499522</v>
+        <v>0.5732269858792975</v>
       </c>
       <c r="T93">
-        <v>6.4713392881109</v>
+        <v>7.260230986774083</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.605061814615333</v>
+        <v>1.587615490543428</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1002522388703438</v>
+        <v>0.1002690957841919</v>
       </c>
       <c r="C94">
-        <v>1075.578728523207</v>
+        <v>911.8734492647091</v>
       </c>
       <c r="D94">
-        <v>13065.57872852321</v>
+        <v>13063.29844926471</v>
       </c>
       <c r="E94">
-        <v>9502.299999999999</v>
+        <v>9663.725000000002</v>
       </c>
       <c r="F94">
-        <v>14851.1</v>
+        <v>15012.525</v>
       </c>
       <c r="G94">
         <v>2861.1</v>
@@ -8995,28 +8995,28 @@
         <v>1787.2</v>
       </c>
       <c r="M94">
-        <v>1125.71338</v>
+        <v>1137.949395</v>
       </c>
       <c r="N94">
-        <v>661.4866199999999</v>
+        <v>649.250605</v>
       </c>
       <c r="O94">
-        <v>145.5270564</v>
+        <v>142.8351331</v>
       </c>
       <c r="P94">
-        <v>515.9595635999999</v>
+        <v>506.4154718999999</v>
       </c>
       <c r="Q94">
-        <v>1659.6595636</v>
+        <v>1650.1154719</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5732269858792975</v>
+        <v>0.646911082631313</v>
       </c>
       <c r="T94">
-        <v>7.260230986774083</v>
+        <v>8.274520313626747</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.587615490543428</v>
+        <v>1.570544356236509</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1002690957841919</v>
+        <v>0.10028595269804</v>
       </c>
       <c r="C95">
-        <v>911.8734492647091</v>
+        <v>748.1689658019895</v>
       </c>
       <c r="D95">
-        <v>13063.29844926471</v>
+        <v>13061.01896580199</v>
       </c>
       <c r="E95">
-        <v>9663.725000000002</v>
+        <v>9825.150000000001</v>
       </c>
       <c r="F95">
-        <v>15012.525</v>
+        <v>15173.95</v>
       </c>
       <c r="G95">
         <v>2861.1</v>
@@ -9077,28 +9077,28 @@
         <v>1787.2</v>
       </c>
       <c r="M95">
-        <v>1137.949395</v>
+        <v>1150.18541</v>
       </c>
       <c r="N95">
-        <v>649.250605</v>
+        <v>637.01459</v>
       </c>
       <c r="O95">
-        <v>142.8351331</v>
+        <v>140.1432098</v>
       </c>
       <c r="P95">
-        <v>506.4154718999999</v>
+        <v>496.8713802</v>
       </c>
       <c r="Q95">
-        <v>1650.1154719</v>
+        <v>1640.5713802</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.646911082631313</v>
+        <v>0.7451565449673336</v>
       </c>
       <c r="T95">
-        <v>8.274520313626747</v>
+        <v>9.626906082763632</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.570544356236509</v>
+        <v>1.553836437553142</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.10028595269804</v>
+        <v>0.1003028096118881</v>
       </c>
       <c r="C96">
-        <v>748.1689658019895</v>
+        <v>584.4652777185293</v>
       </c>
       <c r="D96">
-        <v>13061.01896580199</v>
+        <v>13058.74027771853</v>
       </c>
       <c r="E96">
-        <v>9825.150000000001</v>
+        <v>9986.575000000001</v>
       </c>
       <c r="F96">
-        <v>15173.95</v>
+        <v>15335.375</v>
       </c>
       <c r="G96">
         <v>2861.1</v>
@@ -9159,28 +9159,28 @@
         <v>1787.2</v>
       </c>
       <c r="M96">
-        <v>1150.18541</v>
+        <v>1162.421425</v>
       </c>
       <c r="N96">
-        <v>637.01459</v>
+        <v>624.7785749999998</v>
       </c>
       <c r="O96">
-        <v>140.1432098</v>
+        <v>137.4512865</v>
       </c>
       <c r="P96">
-        <v>496.8713802</v>
+        <v>487.3272884999999</v>
       </c>
       <c r="Q96">
-        <v>1640.5713802</v>
+        <v>1631.0272885</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7451565449673336</v>
+        <v>0.8827001922377629</v>
       </c>
       <c r="T96">
-        <v>9.626906082763632</v>
+        <v>11.52024615955528</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.553836437553142</v>
+        <v>1.537480264526267</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1003028096118881</v>
+        <v>0.1003196665257362</v>
       </c>
       <c r="C97">
-        <v>584.4652777185293</v>
+        <v>420.762384598107</v>
       </c>
       <c r="D97">
-        <v>13058.74027771853</v>
+        <v>13056.46238459811</v>
       </c>
       <c r="E97">
-        <v>9986.575000000001</v>
+        <v>10148</v>
       </c>
       <c r="F97">
-        <v>15335.375</v>
+        <v>15496.8</v>
       </c>
       <c r="G97">
         <v>2861.1</v>
@@ -9241,28 +9241,28 @@
         <v>1787.2</v>
       </c>
       <c r="M97">
-        <v>1162.421425</v>
+        <v>1174.65744</v>
       </c>
       <c r="N97">
-        <v>624.7785749999998</v>
+        <v>612.5425599999999</v>
       </c>
       <c r="O97">
-        <v>137.4512865</v>
+        <v>134.7593632</v>
       </c>
       <c r="P97">
-        <v>487.3272884999999</v>
+        <v>477.7831967999999</v>
       </c>
       <c r="Q97">
-        <v>1631.0272885</v>
+        <v>1621.4831968</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8827001922377629</v>
+        <v>1.089015663143406</v>
       </c>
       <c r="T97">
-        <v>11.52024615955528</v>
+        <v>14.36025627474274</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.537480264526267</v>
+        <v>1.521464845104118</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1003196665257362</v>
+        <v>0.1003365234395843</v>
       </c>
       <c r="C98">
-        <v>420.7623845981034</v>
+        <v>257.06028602478</v>
       </c>
       <c r="D98">
-        <v>13056.4623845981</v>
+        <v>13054.18528602478</v>
       </c>
       <c r="E98">
-        <v>10148</v>
+        <v>10309.425</v>
       </c>
       <c r="F98">
-        <v>15496.8</v>
+        <v>15658.225</v>
       </c>
       <c r="G98">
         <v>2861.1</v>
@@ -9323,28 +9323,28 @@
         <v>1787.2</v>
       </c>
       <c r="M98">
-        <v>1174.65744</v>
+        <v>1186.893455</v>
       </c>
       <c r="N98">
-        <v>612.5425600000001</v>
+        <v>600.3065449999999</v>
       </c>
       <c r="O98">
-        <v>134.7593632</v>
+        <v>132.0674399</v>
       </c>
       <c r="P98">
-        <v>477.7831968</v>
+        <v>468.2391051</v>
       </c>
       <c r="Q98">
-        <v>1621.4831968</v>
+        <v>1611.9391051</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.089015663143404</v>
+        <v>1.432874781319475</v>
       </c>
       <c r="T98">
-        <v>14.3602562747427</v>
+        <v>19.09360646672179</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.521464845104118</v>
+        <v>1.505779640515416</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1003365234395843</v>
+        <v>0.1112078603534324</v>
       </c>
       <c r="C99">
-        <v>257.06028602478</v>
+        <v>-1224.201365586423</v>
       </c>
       <c r="D99">
-        <v>13054.18528602478</v>
+        <v>11734.34863441358</v>
       </c>
       <c r="E99">
-        <v>10309.425</v>
+        <v>10470.85</v>
       </c>
       <c r="F99">
-        <v>15658.225</v>
+        <v>15819.65</v>
       </c>
       <c r="G99">
         <v>2861.1</v>
@@ -9405,45 +9405,45 @@
         <v>1787.2</v>
       </c>
       <c r="M99">
-        <v>1186.893455</v>
+        <v>1423.7685</v>
       </c>
       <c r="N99">
-        <v>600.3065449999999</v>
+        <v>363.4315000000001</v>
       </c>
       <c r="O99">
-        <v>132.0674399</v>
+        <v>79.95493000000003</v>
       </c>
       <c r="P99">
-        <v>468.2391051</v>
+        <v>283.4765700000001</v>
       </c>
       <c r="Q99">
-        <v>1611.9391051</v>
+        <v>1427.17657</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.432874781319475</v>
+        <v>2.120593017671617</v>
       </c>
       <c r="T99">
-        <v>19.09360646672179</v>
+        <v>28.56030685067996</v>
       </c>
       <c r="U99">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V99">
         <v>0.22</v>
       </c>
       <c r="W99">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y99">
-        <v>1.505779640515416</v>
+        <v>1.255260247715833</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1112078603534324</v>
+        <v>0.1355518880685515</v>
       </c>
       <c r="C100">
-        <v>-1224.201365586423</v>
+        <v>-3551.863994976999</v>
       </c>
       <c r="D100">
-        <v>11734.34863441358</v>
+        <v>9568.111005023002</v>
       </c>
       <c r="E100">
-        <v>10470.85</v>
+        <v>10632.275</v>
       </c>
       <c r="F100">
-        <v>15819.65</v>
+        <v>15981.075</v>
       </c>
       <c r="G100">
         <v>2861.1</v>
@@ -9487,129 +9487,47 @@
         <v>1787.2</v>
       </c>
       <c r="M100">
-        <v>1423.7685</v>
+        <v>1895.355495</v>
       </c>
       <c r="N100">
-        <v>363.4315000000001</v>
+        <v>-108.1554950000002</v>
       </c>
       <c r="O100">
-        <v>79.95493000000003</v>
+        <v>-23.79420890000004</v>
       </c>
       <c r="P100">
-        <v>283.4765700000001</v>
+        <v>-84.36128610000016</v>
       </c>
       <c r="Q100">
-        <v>1427.17657</v>
+        <v>1059.3387139</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.120593017671617</v>
+        <v>4.249495791522943</v>
       </c>
       <c r="T100">
-        <v>28.56030685067996</v>
+        <v>57.86545486235544</v>
       </c>
       <c r="U100">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.22</v>
+        <v>0.2074460443105424</v>
       </c>
       <c r="W100">
-        <v>0.0702</v>
+        <v>0.09399689914476968</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.255260247715833</v>
+        <v>0.9429365650479199</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1355518880685515</v>
-      </c>
-      <c r="C101">
-        <v>-3551.863994976999</v>
-      </c>
-      <c r="D101">
-        <v>9568.111005023002</v>
-      </c>
-      <c r="E101">
-        <v>10632.275</v>
-      </c>
-      <c r="F101">
-        <v>15981.075</v>
-      </c>
-      <c r="G101">
-        <v>2861.1</v>
-      </c>
-      <c r="H101">
-        <v>10793.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2930.9</v>
-      </c>
-      <c r="K101">
-        <v>1143.7</v>
-      </c>
-      <c r="L101">
-        <v>1787.2</v>
-      </c>
-      <c r="M101">
-        <v>1895.355495</v>
-      </c>
-      <c r="N101">
-        <v>-108.1554950000002</v>
-      </c>
-      <c r="O101">
-        <v>-23.79420890000004</v>
-      </c>
-      <c r="P101">
-        <v>-84.36128610000016</v>
-      </c>
-      <c r="Q101">
-        <v>1059.3387139</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.249495791522943</v>
-      </c>
-      <c r="T101">
-        <v>57.86545486235544</v>
-      </c>
-      <c r="U101">
-        <v>0.1186</v>
-      </c>
-      <c r="V101">
-        <v>0.2074460443105424</v>
-      </c>
-      <c r="W101">
-        <v>0.09399689914476968</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9429365650479199</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
